--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -41,32 +41,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,46 +140,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -807,20 +777,20 @@
       <c r="C4" s="3" t="n">
         <v>351.3</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="10" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="10" t="n">
         <v>22.7</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="10" t="n">
         <v>28.1</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="10" t="n">
         <v>10.8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.6</v>
@@ -856,10 +826,10 @@
         <v>28.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>156.1</v>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v>22</v>
+        <v>56.1</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>28.6</v>
@@ -871,7 +841,7 @@
         <v>29.1</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>74.3</v>
+        <v>142.3</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>2.1</v>
@@ -892,16 +862,16 @@
       <c r="C5" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G5" s="9" t="n">
+      <c r="D5" s="10" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G5" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -914,13 +884,13 @@
         <v>3.1</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1.9</v>
+        <v>19.1</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>20.4</v>
+        <v>21.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>25.4</v>
@@ -929,22 +899,22 @@
         <v>92</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>26</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>7.4</v>
+        <v>0.4</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>22</v>
@@ -959,7 +929,7 @@
         <v>92</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>2.1</v>
+        <v>9.4</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -977,16 +947,16 @@
       <c r="C6" s="3" t="n">
         <v>368</v>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="G6" s="9" t="n">
+      <c r="D6" s="10" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="G6" s="10" t="n">
         <v>10.3</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -999,7 +969,7 @@
         <v>3.5</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>21.6</v>
@@ -1011,7 +981,7 @@
         <v>25.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>98.8</v>
+        <v>988.5</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0.7</v>
@@ -1023,7 +993,7 @@
         <v>24.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>27.3</v>
+        <v>22.3</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>59.6</v>
@@ -1037,14 +1007,14 @@
       <c r="W6" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="X6" s="3" t="n">
-        <v>29</v>
+      <c r="X6" s="12" t="n">
+        <v>92</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>75.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1062,74 +1032,74 @@
       <c r="C7" s="3" t="n">
         <v>418.2</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="10" t="n">
         <v>32.4</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="10" t="n">
         <v>26.7</v>
       </c>
-      <c r="G7" s="9" t="n">
-        <v>11.4</v>
+      <c r="G7" s="10" t="n">
+        <v>11.5</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>19.4</v>
+        <v>20.6</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>2.1</v>
+        <v>34.5</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>5.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>21.1</v>
+        <v>22.1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>20.9</v>
+        <v>21.7</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>24.6</v>
+        <v>25.7</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>96.5</v>
+        <v>6.5</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q7" s="8" t="n">
-        <v>11.9</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>33.3</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>28</v>
+        <v>25.6</v>
+      </c>
+      <c r="S7" s="12" t="n">
+        <v>72.90000000000001</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>59.5</v>
+        <v>54.8</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>19.1</v>
+        <v>23</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>28.7</v>
+        <v>28.1</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>28.8</v>
+        <v>28.4</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>73.2</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1147,74 +1117,74 @@
       <c r="C8" s="3" t="n">
         <v>368</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="10" t="n">
         <v>33.3</v>
       </c>
-      <c r="E8" s="9" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>11.5</v>
+      <c r="E8" s="10" t="n">
+        <v>-62.4</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>-79.3</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>54.3</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>20.6</v>
+        <v>60.8</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>5.8</v>
+        <v>20.9</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>22.1</v>
+        <v>2</v>
+      </c>
+      <c r="L8" s="12" t="n">
+        <v>9.4</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>21.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>25.7</v>
+        <v>28.2</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>812.1</v>
+        <v>870.6</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>33.3</v>
+        <v>344.6</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="S8" s="3" t="n">
-        <v>27.9</v>
+        <v>24.4</v>
+      </c>
+      <c r="S8" s="12" t="n">
+        <v>57.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>54.8</v>
+        <v>308</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v>28.1</v>
+        <v>96.09999999999999</v>
+      </c>
+      <c r="V8" s="12" t="n">
+        <v>35.2</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>24.4</v>
+        <v>20</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>28.2</v>
+        <v>39.5</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>74.2</v>
+        <v>389.1</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>41.8</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1232,77 +1202,77 @@
       <c r="C9" s="3" t="n">
         <v>1783.6</v>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>161.7</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>107.4</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>134.5</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>54.3</v>
+      <c r="D9" s="10" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>10.8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1.8</v>
+        <v>26.4</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>20.9</v>
+        <v>4.2</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>109.4</v>
+        <v>21.9</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>2.2</v>
+        <v>21.6</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.3</v>
+        <v>25.6</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>3.1</v>
+        <v>927.4</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 066
+</t>
+        </is>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>155.6</v>
+        <v>344.6</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>44.4</v>
+        <v>24.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">308 10
-</t>
-        </is>
+        <v>4.5</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>61.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>12</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>135.7</v>
+        <v>2.1</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>24</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>29.5</v>
+        <v>272.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>389.1</v>
+        <v>22.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>41.8</v>
+        <v>8.4</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1320,72 +1290,74 @@
       <c r="C10" s="3" t="n">
         <v>356.7</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="10" t="n">
         <v>32.3</v>
       </c>
-      <c r="E10" s="9" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>10.8</v>
+      <c r="E10" s="10" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>13.4</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>20.2</v>
+        <v>18.7</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.4</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
+        <v>0.7</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="L10" s="3" t="n">
-        <v>21.9</v>
+        <v>20.6</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>21.6</v>
+        <v>22.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>25.6</v>
+        <v>24</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>1.1</v>
+        <v>29</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>31.1</v>
+        <v>33.2</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>24.9</v>
+        <v>25.8</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>27.5</v>
+        <v>28.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>18</v>
+        <v>563.5</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>27.1</v>
+        <v>29.5</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>24</v>
+        <v>25.1</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>27.9</v>
+        <v>29</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>77.8</v>
+        <v>9.4</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>8.4</v>
+        <v>2.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1401,76 +1373,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>420.3</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>33.13</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>88.7</v>
+        <v>426.3</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>20.5</v>
+        <v>20.1</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>24.8</v>
+        <v>23.3</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q11" s="8" t="n">
-        <v>933.2</v>
+        <v>0.7</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>32.8</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>56.3</v>
+        <v>58</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v>29.5</v>
+        <v>20.8</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>25.1</v>
+        <v>25.6</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>29</v>
+        <v>30.3</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>10.4</v>
+        <v>3.2</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1488,74 +1460,74 @@
       <c r="C12" s="3" t="n">
         <v>418.2</v>
       </c>
-      <c r="D12" s="9" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>12.6</v>
+      <c r="D12" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>18.6</v>
+        <v>19.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>4.8</v>
+        <v>11.6</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>20.4</v>
+        <v>21.3</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="N12" s="8" t="n">
-        <v>23.3</v>
+        <v>21</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>210.4</v>
+        <v>97</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.7</v>
+        <v>67.2</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>32.8</v>
+        <v>29.1</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>25.8</v>
+        <v>24.3</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>28.7</v>
+        <v>27.3</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>158</v>
+        <v>62.9</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>20.8</v>
+        <v>13</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>29.6</v>
+        <v>26.4</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="X12" s="3" t="n">
-        <v>30.3</v>
+        <v>23.8</v>
+      </c>
+      <c r="X12" s="12" t="n">
+        <v>72.8</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>73.2</v>
+        <v>80.8</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>11.1</v>
+        <v>6.6</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1571,76 +1543,76 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>8.300000000000001</v>
+        <v>2362.1</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>8.1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>19.6</v>
+        <v>17.8</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>97</v>
+        <v>998</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v>29.1</v>
+        <v>8.4</v>
+      </c>
+      <c r="Q13" s="12" t="n">
+        <v>72.3</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>27.3</v>
+        <v>28.2</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>27.8</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>13</v>
+        <v>8.1</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>26.4</v>
+        <v>26</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>27.8</v>
+        <v>28.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>80.8</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1656,76 +1628,80 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>121.4</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>17.8</v>
+        <v>0.6</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+1
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0</v>
+        <v>4.8</v>
+      </c>
+      <c r="K14" s="12" t="n">
+        <v>60.6</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>21.1</v>
+        <v>13.5</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>20.9</v>
+        <v>19.4</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>24.6</v>
+        <v>22.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>98</v>
+        <v>9.6</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>27.3</v>
+        <v>6.2</v>
+      </c>
+      <c r="Q14" s="12" t="n">
+        <v>60</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>24.2</v>
+        <v>25.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>28.2</v>
+        <v>30</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>77.8</v>
+        <v>41</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>8.1</v>
+        <v>12.3</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>24</v>
+        <v>21.9</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>28.6</v>
+        <v>24.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1743,74 +1719,74 @@
       <c r="C15" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="E15" s="9" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>12.1</v>
+      <c r="E15" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>54.5</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>17.4</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>20.5</v>
+        <v>2.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>4</v>
+        <v>19.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>19.5</v>
+        <v>0.1</v>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>2.9</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>22.4</v>
+        <v>7.3</v>
+      </c>
+      <c r="N15" s="12" t="n">
+        <v>33.7</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>99</v>
+        <v>496</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>30</v>
+        <v>2.2</v>
+      </c>
+      <c r="Q15" s="12" t="n">
+        <v>51.4</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>30</v>
+        <v>42.7</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>71</v>
+        <v>331</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="V15" s="3" t="n">
-        <v>25</v>
+        <v>76.3</v>
+      </c>
+      <c r="V15" s="12" t="n">
+        <v>36.5</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>21.9</v>
+        <v>1.4</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>24.3</v>
+        <v>75.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>386.1</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>3.4</v>
+        <v>42.4</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1826,76 +1802,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>5304.1</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>154</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>99</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>126.8</v>
-      </c>
-      <c r="G16" s="3" t="n">
+        <v>1530.8</v>
+      </c>
+      <c r="D16" s="13" t="n">
         <v>54.5</v>
       </c>
+      <c r="E16" s="13" t="n">
+        <v>199.2</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>10.7</v>
+      </c>
       <c r="H16" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>18.4</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>14.6</v>
+        <v>11.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>19.7</v>
+        <v>32.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>16.4</v>
+        <v>4.7</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>28.9</v>
+        <v>206.6</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.9</v>
+        <v>20.4</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>23.8</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>490</v>
+        <v>98</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>152.4</v>
+        <v>3606.5</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>85.8</v>
+        <v>25.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.4</v>
+        <v>28.5</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>331</v>
+        <v>66.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>176.3</v>
+        <v>15.3</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>136.5</v>
+        <v>22.3</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1.4</v>
+        <v>24.1</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>386.1</v>
+        <v>725.6</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>4.2</v>
+        <v>8.5</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1911,76 +1887,76 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>306.2</v>
-      </c>
-      <c r="D17" s="9" t="n">
+        <v>606.4</v>
+      </c>
+      <c r="D17" s="13" t="n">
         <v>30.8</v>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>10.9</v>
+      <c r="E17" s="13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>18.4</v>
+        <v>17.5</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>51.9</v>
+        <v>4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>20.4</v>
+        <v>19.2</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>39.4</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>23.8</v>
+        <v>22.3</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>1.4</v>
+        <v>6.7</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>30.5</v>
+        <v>32.2</v>
       </c>
       <c r="R17" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W17" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="S17" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>6.4</v>
-      </c>
       <c r="X17" s="3" t="n">
-        <v>22.9</v>
+        <v>6.1</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1996,76 +1972,76 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>17.2</v>
+        <v>336.5</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="8" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>19.4</v>
+        <v>42.1</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>22.3</v>
+        <v>24.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>10.7</v>
+        <v>15.4</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>32.2</v>
+        <v>31.1</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>25.3</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>27.8</v>
+        <v>28.2</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>58</v>
+        <v>60.5</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>20.1</v>
+        <v>18.4</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>28.3</v>
+        <v>25.2</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>25.1</v>
+        <v>0.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>29.8</v>
+        <v>29.2</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>21.6</v>
+        <v>88.5</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>8.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2081,76 +2057,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>326.2</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="G19" s="9" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>18.8</v>
+        <v>299</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>4.2</v>
+        <v>42.1</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>20.9</v>
+        <v>19.8</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>20.7</v>
+        <v>19.2</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>10.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>21.7</v>
+        <v>2.9</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>25.3</v>
+        <v>23.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>28.2</v>
+        <v>26.9</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>60.5</v>
+        <v>1.6</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v>25.7</v>
+        <v>10.6</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>25</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>24.2</v>
+        <v>22.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>29.2</v>
+        <v>26.3</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>88.5</v>
+        <v>83</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2166,76 +2142,76 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>299</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>88.40000000000001</v>
+        <v>35.5</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>6.4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>19.8</v>
+        <v>18.4</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>19.7</v>
+        <v>18.9</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>99</v>
+        <v>1006.8</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.2</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>27.9</v>
+        <v>30.1</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>10.6</v>
+        <v>15.7</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>22.8</v>
+        <v>26.3</v>
+      </c>
+      <c r="W20" s="12" t="n">
+        <v>42.4</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>26.3</v>
+        <v>6.6</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>83</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>51.4</v>
+        <v>35.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2251,37 +2227,40 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>357.5</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>12.1</v>
+        <v>294.9</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>6.4</v>
+        <v>12.4</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>18.9</v>
+        <v>3.5</v>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61 1
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>22.1</v>
@@ -2290,37 +2269,37 @@
         <v>100</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>30.1</v>
+        <v>31</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>24.4</v>
+        <v>25.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>26.9</v>
+        <v>22.9</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>63.1</v>
+        <v>66.8</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>15.7</v>
+        <v>14.8</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>463.1</v>
+        <v>24</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>24.2</v>
+        <v>22.6</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>28.8</v>
+        <v>26.5</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2336,76 +2315,76 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>294.9</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="F22" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>494</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q22" s="12" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="R22" s="12" t="n">
         <v>24.6</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L22" s="8" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>25.8</v>
-      </c>
       <c r="S22" s="3" t="n">
-        <v>29.9</v>
+        <v>39.7</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>166.8</v>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="V22" s="3" t="n">
-        <v>24</v>
+        <v>320</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="V22" s="12" t="n">
+        <v>29.3</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>22.6</v>
+        <v>78.3</v>
       </c>
       <c r="X22" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Y22" s="3" t="n">
+        <v>442</v>
+      </c>
+      <c r="Z22" s="3" t="n">
         <v>26.5</v>
-      </c>
-      <c r="Y22" s="3" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v>3.3</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2421,76 +2400,79 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1610.1</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>156</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>125.5</v>
+        <v>322</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>25.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>59.8</v>
+        <v>11.9</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>88.2</v>
+        <v>17.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>18.4</v>
+        <v>2.1</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 2
+</t>
+        </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>6.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>198.5</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>972.8</v>
+        <v>19.6</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>122.7</v>
+        <v>22.7</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>494</v>
+        <v>98.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1252.9</v>
+        <v>30.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1911.6</v>
+        <v>24.9</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>3941.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>320</v>
+        <v>64</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>15.9</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>1899.3</v>
+        <v>25.9</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>18.9</v>
+        <v>23.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>405.6</v>
+        <v>28.1</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>422</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>26.5</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2506,68 +2488,81 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>322</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="G24" s="9" t="n">
-        <v>11.9</v>
+        <v>0.1</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>10.3</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.6</v>
+        <v>18.6</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="8" t="n">
-        <v>117</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 2
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>351.6</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+15156
+</t>
+        </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" s="3" t="n"/>
       <c r="R24" s="3" t="n">
-        <v>24.9</v>
+        <v>0.1</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="X24" s="3" t="n"/>
+        <v>0.1</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="Y24" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2583,58 +2578,64 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>177.8</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>10.3</v>
+        <v>12.8</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>11.2</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I25" s="3" t="n"/>
+        <v>18.6</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="J25" s="3" t="n">
-        <v>41.3</v>
+        <v>0.3</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>31.6</v>
+        <v>14.4</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M25" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N25" s="3" t="n">
+      <c r="M25" s="12" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="N25" s="12" t="n">
         <v>22.9</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P25" s="3" t="n"/>
+      <c r="P25" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q25" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R25" s="3" t="n"/>
+        <v>6.9</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>22.1</v>
+      </c>
       <c r="S25" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>93.59999999999999</v>
+        <v>23.6</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>15.2</v>
+        <v>1.8</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>21</v>
@@ -2643,10 +2644,10 @@
         <v>24.5</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>95.2</v>
+        <v>952.6</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2664,35 +2665,35 @@
       <c r="C26" s="3" t="n">
         <v>345</v>
       </c>
-      <c r="D26" s="9" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G26" s="9" t="n">
-        <v>11.2</v>
+      <c r="D26" s="3" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>68.61</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>13.7</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>18.6</v>
+        <v>12.6</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>20.6</v>
+        <v>26.6</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>20.4</v>
+        <v>26.4</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>23.8</v>
@@ -2701,13 +2702,13 @@
         <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>31.4</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>24.8</v>
+        <v>24.1</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>25.3</v>
@@ -2715,23 +2716,23 @@
       <c r="T26" s="3" t="n">
         <v>55.2</v>
       </c>
-      <c r="U26" s="3" t="n">
-        <v>20.6</v>
+      <c r="U26" s="12" t="n">
+        <v>6.6</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>27.2</v>
+        <v>22.2</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>16.2</v>
+        <v>26.8</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>74.3</v>
+        <v>4.3</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2747,46 +2748,46 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>418.2</v>
+        <v>48.2</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>32.9</v>
+        <v>32.6</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="F27" s="12" t="n">
-        <v>86.09999999999999</v>
+      <c r="F27" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>18.7</v>
+        <v>12.8</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>17.6</v>
+        <v>18.4</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>15.2</v>
+        <v>52.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M27" s="8" t="n">
+      <c r="M27" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>99</v>
+        <v>994</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>32.9</v>
@@ -2807,16 +2808,16 @@
         <v>29.3</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>25.5</v>
+        <v>65.5</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>30.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>74.2</v>
+        <v>0.2</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2834,47 +2835,47 @@
       <c r="C28" s="3" t="n">
         <v>282.3</v>
       </c>
-      <c r="D28" s="9" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E28" s="9" t="n">
+      <c r="D28" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E28" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F28" s="9" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="G28" s="9" t="n">
-        <v>12.8</v>
+      <c r="F28" s="3" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>18.4</v>
+        <v>190.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="8" t="n">
-        <v>220.1</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>19.9</v>
+        <v>18.1</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="M28" s="12" t="n">
+        <v>29.9</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>29.7</v>
+        <v>29.2</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>25.1</v>
@@ -2886,7 +2887,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>12.7</v>
+        <v>14.7</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>24.4</v>
@@ -2898,10 +2899,10 @@
         <v>26.3</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2919,29 +2920,29 @@
       <c r="C29" s="3" t="n">
         <v>140.2</v>
       </c>
-      <c r="D29" s="9" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>24.8</v>
+      <c r="D29" s="15" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>18.9</v>
+        <v>5.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>19</v>
+        <v>2.2</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.1</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>23.7</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>21.9</v>
@@ -2956,7 +2957,7 @@
         <v>96.5</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.9</v>
+        <v>6.9</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>28.6</v>
@@ -2968,7 +2969,7 @@
         <v>28.8</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>73.7</v>
+        <v>3.7</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>10.3</v>
@@ -2983,10 +2984,10 @@
         <v>25.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>24.2</v>
+        <v>21.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>5.8</v>
+        <v>30.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -3004,53 +3005,53 @@
       <c r="C30" s="3" t="n">
         <v>1363.5</v>
       </c>
-      <c r="D30" s="21" t="n">
-        <v>1506.5</v>
-      </c>
-      <c r="E30" s="21" t="n">
-        <v>99</v>
-      </c>
-      <c r="F30" s="21" t="n">
-        <v>28</v>
+      <c r="D30" s="13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>996.1</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>25.6</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>56.9</v>
+        <v>1.4</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>92.2</v>
+        <v>0.4</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>17.9</v>
+        <v>172.1</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>23.7</v>
+        <v>5.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>102.2</v>
+        <v>20.4</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>10.1</v>
+        <v>11.1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.7</v>
+        <v>172.8</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>489.5</v>
+        <v>429.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>145.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>3545.1</v>
+        <v>3.3</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>344.5</v>
@@ -3059,19 +3060,23 @@
         <v>68.8</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>22.1</v>
+        <v>22.4</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="X30" s="3" t="n">
-        <v>26.7</v>
+        <v>15.3</v>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+4
+</t>
+        </is>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>411.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>30.9</v>
+        <v>0.4</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3089,54 +3094,59 @@
       <c r="C31" s="3" t="n">
         <v>272.7</v>
       </c>
-      <c r="D31" s="9" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>25.6</v>
+      <c r="D31" s="15" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>16</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1.1</v>
+        <v>8.6</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="n">
+        <v>34.1</v>
+      </c>
       <c r="L31" s="3" t="n">
-        <v>20.4</v>
+        <v>61.6</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>71.8</v>
+        <v>26.2</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>978.9</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q31" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>84.2</v>
+      <c r="Q31" s="12" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="R31" s="12" t="n">
+        <v>42.4</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>22.1</v>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 89
+</t>
+        </is>
       </c>
       <c r="U31" s="3" t="n">
         <v>13.8</v>
@@ -3145,16 +3155,21 @@
         <v>25.5</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>23.1</v>
+        <v>0.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v>82.3</v>
+        <v>2.1</v>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1141
+22
+171971191 7
+</t>
+        </is>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3172,32 +3187,32 @@
       <c r="C32" s="3" t="n">
         <v>263.5</v>
       </c>
-      <c r="D32" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="E32" s="9" t="n">
+      <c r="D32" s="3" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E32" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="G32" s="9" t="n">
-        <v>8.6</v>
+      <c r="G32" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>21.6</v>
+        <v>20.8</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>21.5</v>
@@ -3208,7 +3223,9 @@
       <c r="O32" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P32" s="3" t="n"/>
+      <c r="P32" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q32" s="3" t="n">
         <v>29</v>
       </c>
@@ -3216,16 +3233,16 @@
         <v>24.5</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>27.9</v>
+        <v>22.9</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>638.2</v>
+        <v>69.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="V32" s="3" t="n">
-        <v>27.1</v>
+      <c r="V32" s="12" t="n">
+        <v>83.09999999999999</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>24.5</v>
@@ -3234,10 +3251,15 @@
         <v>25.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>6.7</v>
+        <v>0.8</v>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1717177
+23
+83
+</t>
+        </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3255,32 +3277,32 @@
       <c r="C33" s="3" t="n">
         <v>44.1</v>
       </c>
-      <c r="D33" s="9" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G33" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>29</v>
+      <c r="D33" s="10" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>10.3</v>
+        <v>1.3</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>20.8</v>
+        <v>2.1</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>20.6</v>
@@ -3289,10 +3311,10 @@
         <v>24.1</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>98</v>
+        <v>980.8</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>0.4</v>
+        <v>20.4</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>24.2</v>
@@ -3301,7 +3323,7 @@
         <v>22.1</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>83.40000000000001</v>
@@ -3319,10 +3341,10 @@
         <v>21.4</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>948.1</v>
+        <v>28.7</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0.3</v>
+        <v>12.8</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3338,47 +3360,52 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E34" s="9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D34" s="15" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="E34" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="F34" s="9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G34" s="9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="I34" s="3" t="n"/>
+      <c r="F34" s="15" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J34" s="3" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>20.1</v>
+        <v>19</v>
+      </c>
+      <c r="M34" s="12" t="n">
+        <v>61.2</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>980.8</v>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 20
+</t>
+        </is>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>30.1</v>
+        <v>32.1</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>25.6</v>
@@ -3387,13 +3414,13 @@
         <v>29.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>70.2</v>
+        <v>76.2</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V34" s="3" t="n">
-        <v>26.3</v>
+      <c r="V34" s="12" t="n">
+        <v>63.5</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>21</v>
@@ -3405,7 +3432,7 @@
         <v>62.5</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>12.8</v>
+        <v>4.9</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3423,38 +3450,44 @@
       <c r="C35" s="3" t="n">
         <v>284.4</v>
       </c>
-      <c r="D35" s="9" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E35" s="9" t="n">
+      <c r="D35" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E35" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="G35" s="9" t="n">
-        <v>10.7</v>
+      <c r="G35" s="3" t="n">
+        <v>2.5</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>1.5</v>
+        <v>19</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 6
+</t>
+        </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 72
+</t>
+        </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>19</v>
+        <v>21.9</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>19</v>
+        <v>0.4</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>20.9</v>
+        <v>25.8</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>100</v>
@@ -3478,7 +3511,7 @@
         <v>9.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>66.3</v>
+        <v>26.3</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>24.4</v>
@@ -3490,7 +3523,7 @@
         <v>85.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3508,29 +3541,39 @@
       <c r="C36" s="3" t="n">
         <v>117.2</v>
       </c>
-      <c r="D36" s="9" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E36" s="9" t="n">
+      <c r="D36" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E36" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="F36" s="9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G36" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>0.6</v>
+      <c r="F36" s="15" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222725
+1142811042
+</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 6
+</t>
+        </is>
       </c>
       <c r="J36" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K36" s="3" t="n">
-        <v>1.3</v>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 72
+</t>
+        </is>
       </c>
       <c r="L36" s="3" t="n">
         <v>21.9</v>
@@ -3539,13 +3582,13 @@
         <v>21.7</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>25.8</v>
+        <v>20.9</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>21.5</v>
@@ -3562,20 +3605,20 @@
       <c r="U36" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="V36" s="3" t="n">
-        <v>21.4</v>
+      <c r="V36" s="12" t="n">
+        <v>41.4</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>2.2</v>
+        <v>24.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>24.2</v>
+        <v>4.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3591,16 +3634,16 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>826.4</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>142.9</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>121.5</v>
+        <v>22.6</v>
+      </c>
+      <c r="D37" s="13" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>1.5</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>42.9</v>
@@ -3612,34 +3655,39 @@
         <v>5.8</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>17.9</v>
+        <v>17.3</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>1203444.6</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>44.4</v>
+        <v>1034.4</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">777
+22
+7
+</t>
+        </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>214.9</v>
+        <v>20.9</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>495</v>
+        <v>425</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>133.1</v>
+        <v>1334.1</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>11287.9</v>
+        <v>117.9</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>27.3</v>
+        <v>86.3</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>393.6</v>
@@ -3651,16 +3699,14 @@
         <v>124.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v>26</v>
-      </c>
+        <v>26.5</v>
+      </c>
+      <c r="X37" s="3" t="n"/>
       <c r="Y37" s="3" t="n">
         <v>416</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3678,23 +3724,23 @@
       <c r="C38" s="3" t="n">
         <v>165.3</v>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="10" t="n">
         <v>24.3</v>
       </c>
-      <c r="G38" s="9" t="n">
-        <v>8.6</v>
+      <c r="G38" s="10" t="n">
+        <v>8.5</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>1.8</v>
@@ -3704,7 +3750,7 @@
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>20.6</v>
+        <v>61.3</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.2</v>
@@ -3713,17 +3759,19 @@
         <v>99</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q38" s="3" t="n"/>
+        <v>6.2</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>26.6</v>
+      </c>
       <c r="R38" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>29.3</v>
+        <v>73.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>78.7</v>
+        <v>78.2</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>8.1</v>
@@ -3732,13 +3780,13 @@
         <v>84.8</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>46.5</v>
+        <v>26.5</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>27.2</v>
+        <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>83.2</v>
+        <v>8324.799999999999</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>5.6</v>
@@ -3757,72 +3805,78 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="D39" s="9" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F39" s="9" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="D39" s="15" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F39" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="G39" s="9" t="n">
+      <c r="G39" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>545.5</v>
+        <v>1.8</v>
       </c>
       <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n">
-        <v>19.5</v>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 29
+15
+</t>
+        </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="N39" s="3" t="n"/>
+        <v>10.6</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="O39" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>30.7</v>
+        <v>10.1</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>28.8</v>
+        <v>89.3</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>15.2</v>
+        <v>666.1</v>
+      </c>
+      <c r="U39" s="12" t="n">
+        <v>42.7</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>28</v>
+        <v>61.2</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>24</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>27.3</v>
+        <v>22.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>23.4</v>
+        <v>2.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3838,76 +3892,74 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>242.6</v>
-      </c>
-      <c r="D40" s="9" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F40" s="9" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="G40" s="9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>19.4</v>
+        <v>28.1</v>
+      </c>
+      <c r="D40" s="15" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="K40" s="3" t="n"/>
       <c r="L40" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>29.2</v>
+        <v>19.5</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>19.5</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>23.2</v>
+        <v>24.6</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>98.8</v>
+        <v>990.6</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>29.3</v>
+        <v>36.7</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>24.9</v>
+        <v>25.3</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>70.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>12</v>
+        <v>15.2</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>27.1</v>
+        <v>28</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>29.1</v>
+        <v>27.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>24.4</v>
+        <v>0.1</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>6.7</v>
+        <v>10.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3923,76 +3975,80 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>288.6</v>
-      </c>
-      <c r="D41" s="9" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F41" s="9" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G41" s="9" t="n">
-        <v>10.5</v>
+        <v>242.6</v>
+      </c>
+      <c r="D41" s="15" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>18.6</v>
+        <v>19.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>11.1</v>
+        <v>8</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="M41" s="8" t="n">
-        <v>29.2</v>
+        <v>21</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">442
+111
+</t>
+        </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>25.2</v>
+        <v>23.2</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>30.9</v>
+        <v>29.3</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>21.7</v>
+        <v>24.9</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>27.6</v>
+        <v>28.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>17</v>
+        <v>20.5</v>
+      </c>
+      <c r="U41" s="12" t="n">
+        <v>26</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>27.1</v>
+        <v>22.1</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>29.3</v>
+        <v>22.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>81.8</v>
+        <v>24.4</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4008,74 +4064,76 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>311.6</v>
-      </c>
-      <c r="D42" s="9" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F42" s="9" t="n">
-        <v>25.9</v>
+        <v>288.6</v>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>25.6</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H42" s="8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H42" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>18.6</v>
+        <v>1.5</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="K42" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="N42" s="12" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>10618.2</v>
+      </c>
+      <c r="P42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="M42" s="3" t="n"/>
-      <c r="N42" s="3" t="n">
+      <c r="Q42" s="3" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="R42" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="O42" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P42" s="3" t="n">
+      <c r="S42" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="Y42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="R42" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Y42" s="3" t="n">
-        <v>84.3</v>
-      </c>
       <c r="Z42" s="3" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4091,29 +4149,31 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>7779.7</v>
-      </c>
-      <c r="D43" s="9" t="n">
+        <v>311.6</v>
+      </c>
+      <c r="D43" s="10" t="n">
         <v>30.8</v>
       </c>
-      <c r="E43" s="9" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F43" s="9" t="n">
-        <v>25.9</v>
+      <c r="E43" s="10" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>25.6</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H43" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H43" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="I43" s="8" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="J43" s="3" t="n"/>
+      <c r="I43" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="K43" s="3" t="n">
-        <v>39.5</v>
+        <v>0.2</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>21.2</v>
@@ -4122,31 +4182,41 @@
       <c r="N43" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="O43" s="3" t="n"/>
+      <c r="O43" s="3" t="n">
+        <v>99</v>
+      </c>
       <c r="P43" s="3" t="n">
-        <v>0.2</v>
+        <v>6.4</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n"/>
+      <c r="R43" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>24</v>
+      </c>
       <c r="T43" s="3" t="n">
-        <v>77</v>
+        <v>726</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n"/>
+      <c r="W43" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>95.09999999999999</v>
+      </c>
       <c r="Y43" s="3" t="n">
-        <v>392.3</v>
+        <v>84.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>32.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4162,55 +4232,79 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>7779.7</v>
-      </c>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="9" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>934.6</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="8" t="n">
-        <v>14.9</v>
-      </c>
+        <v>311.6</v>
+      </c>
+      <c r="D44" s="15" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G44" s="15" t="n">
+        <v>546.5</v>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42424
+211
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L44" s="8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="n"/>
-      <c r="O44" s="3" t="n">
-        <v>491.8</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+111562
+</t>
+        </is>
+      </c>
+      <c r="N44" s="12" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="O44" s="3" t="n"/>
       <c r="P44" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q44" s="8" t="n">
-        <v>2461.2</v>
-      </c>
-      <c r="R44" s="3" t="n"/>
-      <c r="S44" s="3" t="n"/>
-      <c r="T44" s="3" t="n"/>
+        <v>6.4</v>
+      </c>
+      <c r="Q44" s="12" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="R44" s="12" t="n">
+        <v>373.3</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>726</v>
+      </c>
       <c r="U44" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="V44" s="3" t="n"/>
-      <c r="W44" s="3" t="n"/>
-      <c r="X44" s="3" t="n"/>
-      <c r="Y44" s="3" t="n"/>
-      <c r="Z44" s="3" t="n">
-        <v>32.3</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="X44" s="12" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="Y44" s="3" t="n">
+        <v>3242.3</v>
+      </c>
+      <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4225,58 +4319,60 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>290.7</v>
-      </c>
-      <c r="D45" s="21" t="n">
-        <v>305.1</v>
-      </c>
-      <c r="E45" s="21" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>155</v>
+        <v>1453.4</v>
+      </c>
+      <c r="D45" s="13" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>779.7</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>153</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>10.1</v>
+        <v>50.6</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>934.6</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J45" s="3" t="n"/>
+      <c r="J45" s="3" t="n">
+        <v>45.9</v>
+      </c>
       <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n"/>
+      <c r="L45" s="3" t="n">
+        <v>113.8</v>
+      </c>
       <c r="M45" s="3" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>24.1</v>
+        <v>4.4</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="P45" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>494.2</v>
+      </c>
+      <c r="P45" s="3" t="n"/>
       <c r="Q45" s="3" t="n">
-        <v>29.3</v>
+        <v>146.3</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>64.5</v>
+        <v>24.5</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>27.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>68.3</v>
+        <v>341.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>13.2</v>
+        <v>66.2</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>26.8</v>
+        <v>71.7</v>
       </c>
       <c r="W45" s="3" t="n">
         <v>23.8</v>
@@ -4285,10 +4381,10 @@
         <v>27.6</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>78.5</v>
+        <v>3242.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>7.7</v>
+        <v>38.3</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4303,56 +4399,78 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="14" t="n"/>
-      <c r="E46" s="14" t="n"/>
-      <c r="F46" s="9" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="G46" s="3" t="n">
+      <c r="C46" s="3" t="n">
+        <v>290.7</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G46" s="10" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="8" t="n">
+      <c r="H46" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>16.7</v>
+        <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n">
-        <v>20.8</v>
+      <c r="K46" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="L46" s="12" t="n">
+        <v>68.40000000000001</v>
       </c>
       <c r="M46" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="S46" s="12" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="U46" s="12" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W46" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="N46" s="3" t="n"/>
-      <c r="O46" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U46" s="3" t="n"/>
-      <c r="V46" s="3" t="n"/>
-      <c r="W46" s="3" t="n"/>
       <c r="X46" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
+        <v>0.1</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>2.7</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -49,12 +61,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -140,28 +146,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -777,74 +789,74 @@
       <c r="C4" s="3" t="n">
         <v>351.3</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="12" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="12" t="n">
         <v>22.7</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="12" t="n">
         <v>28.1</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="12" t="n">
         <v>10.8</v>
       </c>
-      <c r="H4" s="3" t="n">
-        <v>6.6</v>
+      <c r="H4" s="8" t="n">
+        <v>21</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2.6</v>
+        <v>21.6</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4.4</v>
+        <v>14.4</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>27.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q4" s="3" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="P4" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q4" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="S4" s="3" t="n">
-        <v>28.1</v>
+      <c r="S4" s="8" t="n">
+        <v>1281.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="V4" s="3" t="n">
+        <v>156.1</v>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="V4" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="X4" s="3" t="n">
+      <c r="X4" s="8" t="n">
         <v>29.1</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>142.3</v>
+        <v>174.3</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>2.1</v>
+        <v>110</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -862,16 +874,16 @@
       <c r="C5" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D5" s="10" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="G5" s="3" t="n">
+      <c r="D5" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G5" s="12" t="n">
         <v>10.3</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -884,52 +896,52 @@
         <v>3.1</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="L5" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L5" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>25.4</v>
+        <v>0.5</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>92</v>
+        <v>198</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q5" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q5" s="8" t="n">
         <v>26</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="S5" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="S5" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V5" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="V5" s="8" t="n">
         <v>22</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X5" s="3" t="n">
+      <c r="X5" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>9.4</v>
+        <v>2.1</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -945,58 +957,56 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>368</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>10.3</v>
+        <v>12368</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>41</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L6" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L6" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" s="8" t="n">
         <v>25.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>988.5</v>
+        <v>197</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q6" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="Q6" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>22.3</v>
+        <v>41.3</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>59.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>18.6</v>
@@ -1004,17 +1014,17 @@
       <c r="V6" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="X6" s="12" t="n">
-        <v>92</v>
+      <c r="X6" s="8" t="n">
+        <v>29</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1032,74 +1042,74 @@
       <c r="C7" s="3" t="n">
         <v>418.2</v>
       </c>
-      <c r="D7" s="10" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="F7" s="10" t="n">
+      <c r="D7" s="12" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F7" s="12" t="n">
         <v>26.7</v>
       </c>
-      <c r="G7" s="10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>20.6</v>
+      <c r="G7" s="12" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>944.4</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>34.5</v>
+        <v>20.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>14.1</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>11.3</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>21.7</v>
+        <v>20.9</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>25.7</v>
+        <v>46.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>6.5</v>
+        <v>1980.8</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="S7" s="12" t="n">
-        <v>72.90000000000001</v>
+        <v>10.4</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>311.9</v>
+      </c>
+      <c r="R7" s="8" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>28</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>23</v>
+        <v>159.5</v>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>28.4</v>
+        <v>28.7</v>
+      </c>
+      <c r="W7" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="X7" s="8" t="n">
+        <v>28.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1115,76 +1125,76 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>368</v>
-      </c>
-      <c r="D8" s="10" t="n">
+        <v>19368</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q8" s="8" t="n">
         <v>33.3</v>
       </c>
-      <c r="E8" s="10" t="n">
-        <v>-62.4</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>-79.3</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" s="12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="N8" s="3" t="n">
+      <c r="R8" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>194.8</v>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="O8" s="3" t="n">
-        <v>870.6</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>344.6</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="S8" s="12" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>308</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>96.09999999999999</v>
-      </c>
-      <c r="V8" s="12" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>39.5</v>
-      </c>
       <c r="Y8" s="3" t="n">
-        <v>389.1</v>
+        <v>74.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>41.8</v>
+        <v>19.8</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1200,79 +1210,58 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1783.6</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>26.4</v>
-      </c>
+        <v>17183.6</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="n">
-        <v>2.4</v>
+        <v>112</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>4.2</v>
+        <v>120.9</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>25.6</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="n">
-        <v>927.4</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 066
-</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>344.6</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>24.9</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
       <c r="S9" s="3" t="n">
-        <v>4.5</v>
+        <v>1371.5</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>61.6</v>
+        <v>908</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W9" s="3" t="n">
-        <v>24</v>
-      </c>
+        <v>190.1</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" s="3" t="inlineStr"/>
       <c r="X9" s="3" t="n">
-        <v>272.9</v>
+        <v>1032.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>22.8</v>
+        <v>1389.1</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>8.4</v>
+        <v>41.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1288,76 +1277,74 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>356.7</v>
-      </c>
-      <c r="D10" s="10" t="n">
+        <v>2356.7</v>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>32.3</v>
       </c>
-      <c r="E10" s="10" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>18.7</v>
+      <c r="E10" s="12" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>20.2</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
+        <v>4.2</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
-        <v>20.6</v>
+        <v>21.9</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>22.5</v>
+        <v>21.6</v>
       </c>
       <c r="N10" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>197.4</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q10" s="8" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="R10" s="8" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="S10" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="W10" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="O10" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>563.5</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>29</v>
+      <c r="X10" s="8" t="n">
+        <v>27.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>9.4</v>
+        <v>177.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>2.2</v>
+        <v>18.4</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1373,76 +1360,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>426.3</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>18.6</v>
+        <v>453.1</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>18.7</v>
       </c>
       <c r="I11" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="K11" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="J11" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L11" s="3" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>23.3</v>
+        <v>24</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>97</v>
+        <v>199</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.7</v>
+        <v>10.2</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>32.8</v>
+        <v>33.2</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="S11" s="3" t="n">
-        <v>28.7</v>
+      <c r="S11" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>25.6</v>
+        <v>156.3</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>655.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>30.3</v>
+        <v>29</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>3.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1458,76 +1445,76 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>418.2</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="E12" s="10" t="n">
+        <v>141824</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>220.3</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>197</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T12" s="3" t="n">
+        <v>1958</v>
+      </c>
+      <c r="U12" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G12" s="10" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="R12" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="S12" s="3" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="T12" s="3" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="V12" s="3" t="n">
-        <v>26.4</v>
+      <c r="V12" s="8" t="n">
+        <v>29.6</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X12" s="12" t="n">
-        <v>72.8</v>
+        <v>25.6</v>
+      </c>
+      <c r="X12" s="8" t="n">
+        <v>30.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>80.8</v>
+        <v>713.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>6.6</v>
+        <v>11.1</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1543,76 +1530,74 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2362.1</v>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>17.8</v>
+        <v>1230.1</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J13" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="M13" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>24.6</v>
+      <c r="K13" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>24.7</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>998</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q13" s="12" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="R13" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="S13" s="3" t="n">
-        <v>28.2</v>
+        <v>197</v>
+      </c>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="8" t="n">
+        <v>229.1</v>
+      </c>
+      <c r="R13" s="8" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>27.3</v>
       </c>
       <c r="T13" s="3" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W13" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X13" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="U13" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="V13" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="W13" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>28.6</v>
-      </c>
       <c r="Y13" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>5</v>
+        <v>16.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1628,80 +1613,76 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-1
-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>1.4</v>
+        <v>1821.4</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>13.5</v>
+        <v>18.6</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>41.1</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>22.4</v>
+        <v>20.9</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>24.6</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>9.6</v>
+        <v>198</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q14" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>25.6</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q14" s="8" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="R14" s="8" t="n">
+        <v>24.8</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>30</v>
+        <v>28.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>41</v>
+        <v>77.8</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>12.3</v>
+        <v>18.1</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>24.3</v>
+        <v>24</v>
+      </c>
+      <c r="X14" s="8" t="n">
+        <v>28.6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1719,74 +1700,74 @@
       <c r="C15" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D15" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>54.5</v>
+      <c r="D15" s="12" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>12.1</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>17.4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2.5</v>
+        <v>94.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L15" s="12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="N15" s="12" t="n">
-        <v>33.7</v>
+        <v>4</v>
+      </c>
+      <c r="K15" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>22.4</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>496</v>
+        <v>199</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q15" s="12" t="n">
-        <v>51.4</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>30</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>42.7</v>
+        <v>25.6</v>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>30</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>331</v>
+        <v>71</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="V15" s="12" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X15" s="3" t="n">
-        <v>75.8</v>
+        <v>12.3</v>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="W15" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="X15" s="8" t="n">
+        <v>24.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>386.1</v>
+        <v>16.6</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>42.4</v>
+        <v>17.4</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1801,77 +1782,59 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>1530.8</v>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="E16" s="13" t="n">
-        <v>199.2</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>10.7</v>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="12" t="n">
+        <v>154</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>15.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>18.4</v>
+        <v>192.1</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>32.9</v>
+        <v>19.7</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>206.6</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>23.8</v>
-      </c>
+        <v>186.4</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr"/>
       <c r="O16" s="3" t="n">
-        <v>98</v>
+        <v>1490</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>3606.5</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>28.5</v>
-      </c>
+        <v>152.4</v>
+      </c>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
       <c r="T16" s="3" t="n">
-        <v>66.8</v>
+        <v>1331</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="V16" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>28</v>
-      </c>
+        <v>176.3</v>
+      </c>
+      <c r="V16" s="3" t="inlineStr"/>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>725.6</v>
+        <v>1386.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>8.5</v>
+        <v>42.3</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1887,76 +1850,72 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>606.4</v>
-      </c>
-      <c r="D17" s="13" t="n">
+        <v>306.2</v>
+      </c>
+      <c r="D17" s="12" t="n">
         <v>30.8</v>
       </c>
-      <c r="E17" s="13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>13</v>
+      <c r="E17" s="12" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>10.9</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>17.5</v>
+        <v>18.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>4.5</v>
+        <v>23.5</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M17" s="12" t="n">
-        <v>39.4</v>
+        <v>20.6</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>22.3</v>
+        <v>23.8</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>41</v>
+        <v>198</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>6.7</v>
+        <v>10.4</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>32.2</v>
+        <v>90.5</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>27.8</v>
+        <v>25.8</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>58</v>
+        <v>166.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>25.1</v>
-      </c>
+        <v>15.3</v>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="W17" s="3" t="inlineStr"/>
       <c r="X17" s="3" t="n">
-        <v>6.1</v>
+        <v>28</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>11.6</v>
+        <v>1717.2</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>8.6</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1972,76 +1931,76 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>336.5</v>
-      </c>
-      <c r="D18" s="15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>18.8</v>
+        <v>332.5</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>67.2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.1</v>
+        <v>20.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>42.1</v>
+        <v>14</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>8.4</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>20.7</v>
+        <v>19.7</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>89.40000000000001</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>24.3</v>
+        <v>22.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>98</v>
+        <v>197</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="R18" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="R18" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="S18" s="3" t="n">
-        <v>28.2</v>
+      <c r="S18" s="8" t="n">
+        <v>27.8</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="U18" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v>25.2</v>
+        <v>158</v>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v>28.3</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="X18" s="3" t="n">
-        <v>29.2</v>
+        <v>25.1</v>
+      </c>
+      <c r="X18" s="8" t="n">
+        <v>229.8</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>88.5</v>
+        <v>177.6</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>3.8</v>
+        <v>8.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2057,76 +2016,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>299</v>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="G19" s="10" t="n">
-        <v>10</v>
+        <v>1326.2</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>11.7</v>
       </c>
       <c r="H19" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="R19" s="8" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="S19" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="U19" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="T19" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="W19" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X19" s="3" t="n">
-        <v>26.3</v>
+      <c r="V19" s="8" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="W19" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>29.2</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>83</v>
+        <v>188.5</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2142,76 +2101,74 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>24.5</v>
+        <v>1299</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>24.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>6.4</v>
+        <v>10</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>18.4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3.8</v>
+        <v>31.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M20" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>1006.8</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>24.4</v>
+      <c r="Q20" s="8" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="R20" s="8" t="n">
+        <v>238.4</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>63.4</v>
+        <v>171.6</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="V20" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X20" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W20" s="12" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="X20" s="3" t="n">
-        <v>6.6</v>
-      </c>
       <c r="Y20" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>183</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>35.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2227,79 +2184,74 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>294.9</v>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="F21" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>12.4</v>
-      </c>
+        <v>1357.5</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61 1
-</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>19.1</v>
+        <v>3.8</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>22.1</v>
+        <v>18.9</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>25.8</v>
+        <v>1001</v>
+      </c>
+      <c r="P21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="8" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="R21" s="8" t="n">
+        <v>24.4</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>22.9</v>
+        <v>26.9</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>66.8</v>
+        <v>163.1</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>14.8</v>
+        <v>15.7</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
+      </c>
+      <c r="W21" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="X21" s="8" t="n">
+        <v>28.8</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>88.8</v>
+        <v>184.1</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2315,76 +2267,74 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="D22" s="15" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>96.09999999999999</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="G22" s="15" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>88.2</v>
+        <v>1294.9</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>531.2</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>17.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>18.4</v>
-      </c>
+        <v>16.9</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr"/>
       <c r="K22" s="3" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>10.1</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>69.09999999999999</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>97.8</v>
+        <v>19.1</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>7.3</v>
+        <v>22.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>494</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q22" s="12" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="R22" s="12" t="n">
-        <v>24.6</v>
+        <v>100</v>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>39.7</v>
+        <v>29.9</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>320</v>
+        <v>166.8</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="V22" s="12" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="X22" s="3" t="n">
-        <v>10.6</v>
+        <v>14.8</v>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="W22" s="8" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="X22" s="8" t="n">
+        <v>216.5</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>442</v>
+        <v>88.8</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>26.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2399,80 +2349,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>322</v>
-      </c>
-      <c r="D23" s="13" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E23" s="13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F23" s="13" t="n">
-        <v>25.5</v>
-      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="16" t="inlineStr"/>
+      <c r="E23" s="16" t="inlineStr"/>
+      <c r="F23" s="16" t="inlineStr"/>
       <c r="G23" s="3" t="n">
-        <v>11.9</v>
+        <v>59.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>17.6</v>
+        <v>88.2</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 2
-</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>65.09999999999999</v>
-      </c>
+        <v>10.4</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
       <c r="L23" s="3" t="n">
-        <v>198.5</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>22.7</v>
-      </c>
+        <v>198.4</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>0.3</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
+        <v>1252.9</v>
+      </c>
+      <c r="R23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="n">
-        <v>64</v>
+        <v>1320</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="V23" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X23" s="3" t="n">
-        <v>28.1</v>
-      </c>
+        <v>179.6</v>
+      </c>
+      <c r="V23" s="3" t="inlineStr"/>
+      <c r="W23" s="3" t="inlineStr"/>
+      <c r="X23" s="3" t="inlineStr"/>
       <c r="Y23" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>422</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>2.2</v>
+        <v>26.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2488,81 +2409,72 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F24" s="10" t="n">
+        <v>322</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="8" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>988.1</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="R24" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G24" s="10" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 2
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>351.6</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-15156
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q24" s="3" t="n"/>
-      <c r="R24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>0.1</v>
+      <c r="S24" s="8" t="n">
+        <v>27.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>0.1</v>
+        <v>164</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>0.4</v>
+        <v>15.9</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>0.1</v>
+        <v>25.9</v>
+      </c>
+      <c r="W24" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>28.1</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>0.1</v>
+        <v>184.4</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>1.1</v>
+        <v>55.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2578,76 +2490,74 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F25" s="10" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G25" s="10" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H25" s="3" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H25" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="I25" s="3" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="3" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>14.4</v>
+        <v>17.6</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M25" s="12" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="N25" s="12" t="n">
+      <c r="M25" s="3" t="n">
+        <v>194.4</v>
+      </c>
+      <c r="N25" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0.4</v>
+        <v>10.4</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>6.9</v>
+        <v>22.9</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="S25" s="3" t="n">
+      <c r="S25" s="8" t="n">
         <v>26.1</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>23.6</v>
+        <v>93.2</v>
       </c>
       <c r="U25" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W25" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="X25" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="Z25" s="3" t="n">
         <v>1.8</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="Y25" s="3" t="n">
-        <v>952.6</v>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v>0.1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2663,43 +2573,41 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>345</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="F26" s="15" t="n">
-        <v>68.61</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>3.1</v>
-      </c>
+        <v>2345</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
       <c r="J26" s="3" t="n">
-        <v>4.4</v>
+        <v>14.4</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>26.6</v>
+        <v>20.6</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>26.4</v>
+        <v>20.4</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0.4</v>
@@ -2707,7 +2615,7 @@
       <c r="Q26" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2716,23 +2624,23 @@
       <c r="T26" s="3" t="n">
         <v>55.2</v>
       </c>
-      <c r="U26" s="12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W26" s="3" t="n">
+      <c r="U26" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="W26" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>26.8</v>
+        <v>62.1</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>4.3</v>
+        <v>174.3</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2748,31 +2656,29 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>32.6</v>
+        <v>2418.2</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>32.9</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>26.8</v>
+        <v>5.4</v>
+      </c>
+      <c r="F27" s="17" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12.8</v>
+        <v>13.7</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>1.9</v>
-      </c>
+        <v>17.6</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
-        <v>52.4</v>
+        <v>5.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>19.6</v>
@@ -2780,26 +2686,26 @@
       <c r="M27" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="N27" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>994</v>
+        <v>199</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>32.9</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="S27" s="3" t="n">
+      <c r="S27" s="8" t="n">
         <v>26.4</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>23.4</v>
@@ -2807,17 +2713,17 @@
       <c r="V27" s="3" t="n">
         <v>29.3</v>
       </c>
-      <c r="W27" s="3" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="X27" s="3" t="n">
+      <c r="W27" s="8" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="X27" s="8" t="n">
         <v>30.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>0.2</v>
+        <v>174.2</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>4.3</v>
+        <v>110.5</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2835,74 +2741,74 @@
       <c r="C28" s="3" t="n">
         <v>282.3</v>
       </c>
-      <c r="D28" s="15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E28" s="3" t="n">
+      <c r="D28" s="12" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E28" s="12" t="n">
         <v>19.8</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>190.8</v>
+      <c r="F28" s="12" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>18.4</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.1</v>
+        <v>11.9</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>18.1</v>
+        <v>12.6</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M28" s="12" t="n">
-        <v>29.9</v>
+      <c r="M28" s="3" t="n">
+        <v>49.9</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>23.1</v>
+        <v>33.4</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>38</v>
+        <v>198</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q28" s="3" t="n">
-        <v>29.2</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q28" s="8" t="n">
+        <v>29.7</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="S28" s="3" t="n">
+      <c r="S28" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>169.4</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="W28" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v>224.4</v>
+      </c>
+      <c r="W28" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="X28" s="3" t="n">
-        <v>26.3</v>
+      <c r="X28" s="8" t="n">
+        <v>260.3</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>5.8</v>
+        <v>14.3</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2918,76 +2824,76 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>140.2</v>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>5.2</v>
+        <v>120.2</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>8.9</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.2</v>
+        <v>19</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>23.7</v>
+        <v>18.1</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="N29" s="8" t="n">
         <v>25.4</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>96.5</v>
+        <v>196.5</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="Q29" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q29" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>3.7</v>
+        <v>173.7</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="V29" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="W29" s="3" t="n">
+      <c r="V29" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="W29" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="X29" s="3" t="n">
+      <c r="X29" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>21.6</v>
+        <v>181.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>30.2</v>
+        <v>5.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -3002,81 +2908,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>1363.5</v>
-      </c>
-      <c r="D30" s="13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E30" s="13" t="n">
-        <v>996.1</v>
-      </c>
-      <c r="F30" s="13" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>1.4</v>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="16" t="inlineStr"/>
+      <c r="E30" s="16" t="inlineStr"/>
+      <c r="F30" s="16" t="inlineStr"/>
+      <c r="G30" s="17" t="n">
+        <v>50.7</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.4</v>
+        <v>192.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2</v>
+        <v>9.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>172.1</v>
+        <v>16.7</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>172.8</v>
-      </c>
+        <v>123.7</v>
+      </c>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>429.5</v>
+        <v>1489.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Q30" s="3" t="n">
-        <v>145.5</v>
-      </c>
-      <c r="R30" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>3.3</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="inlineStr"/>
       <c r="T30" s="3" t="n">
-        <v>344.5</v>
+        <v>1344.5</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="V30" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="W30" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-4
-</t>
-        </is>
-      </c>
+        <v>168.8</v>
+      </c>
+      <c r="V30" s="3" t="inlineStr"/>
+      <c r="W30" s="3" t="inlineStr"/>
+      <c r="X30" s="3" t="inlineStr"/>
       <c r="Y30" s="3" t="n">
-        <v>11.5</v>
+        <v>1411.5</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>0.4</v>
+        <v>30.9</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3094,82 +2970,72 @@
       <c r="C31" s="3" t="n">
         <v>272.7</v>
       </c>
-      <c r="D31" s="15" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="E31" s="13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F31" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>19.4</v>
+      <c r="D31" s="12" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>88.40000000000001</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1.3</v>
+        <v>20.1</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="N31" s="3" t="n">
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="M31" s="8" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="N31" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>978.9</v>
+        <v>197.9</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q31" s="12" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="R31" s="12" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="T31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6 89
-</t>
-        </is>
+        <v>10.2</v>
+      </c>
+      <c r="Q31" s="8" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="R31" s="8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S31" s="8" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>168.9</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>13.8</v>
+        <v>63.8</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="W31" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1141
-22
-171971191 7
-</t>
-        </is>
+        <v>255.1</v>
+      </c>
+      <c r="W31" s="8" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X31" s="8" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>181.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>6.1</v>
+        <v>16.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3185,81 +3051,74 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>263.5</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E32" s="3" t="n">
+        <v>1263.5</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="E32" s="12" t="n">
         <v>20.4</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="12" t="n">
         <v>24.7</v>
       </c>
-      <c r="G32" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>19</v>
+      <c r="G32" s="12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>16.3</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="3" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="M32" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="M32" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="N32" s="3" t="n">
+      <c r="N32" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>99</v>
+        <v>990.1</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="S32" s="3" t="n">
-        <v>22.9</v>
+      <c r="S32" s="8" t="n">
+        <v>27.9</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>69.8</v>
+        <v>169.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="V32" s="12" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="W32" s="3" t="n">
+      <c r="V32" s="8" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="W32" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="X32" s="3" t="n">
-        <v>25.8</v>
+      <c r="X32" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1717177
-23
-83
-</t>
-        </is>
+        <v>181.1</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>16.7</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3275,76 +3134,72 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F33" s="10" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G33" s="10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>17.8</v>
+        <v>144.1</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>129</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>1.3</v>
-      </c>
+        <v>10.5</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr"/>
       <c r="K33" s="3" t="n">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>2.1</v>
+        <v>20.8</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="N33" s="3" t="n">
+      <c r="N33" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>980.8</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>20.4</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="P33" s="3" t="inlineStr"/>
       <c r="Q33" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="S33" s="3" t="n">
-        <v>1.5</v>
+      <c r="S33" s="8" t="n">
+        <v>25.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>183.4</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="X33" s="3" t="n">
-        <v>21.4</v>
+      <c r="X33" s="8" t="n">
+        <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>28.7</v>
+        <v>191.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>12.8</v>
+        <v>2.3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3360,79 +3215,74 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D34" s="15" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="F34" s="15" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>13.6</v>
+        <v>1117.8</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>167.8</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr"/>
       <c r="K34" s="3" t="n">
-        <v>2.8</v>
+        <v>5.9</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <v>61.2</v>
+        <v>20.1</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>980.8</v>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 20
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="R34" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" s="8" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="R34" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>76.2</v>
+        <v>70.2</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V34" s="12" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="W34" s="3" t="n">
+      <c r="V34" s="8" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="W34" s="8" t="n">
         <v>21</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>29.3</v>
+        <v>21.4</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>62.5</v>
+        <v>162.5</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>4.9</v>
+        <v>12.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3448,64 +3298,56 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>284.4</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E35" s="3" t="n">
+        <v>1284.4</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E35" s="12" t="n">
         <v>18.8</v>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="12" t="n">
         <v>24.1</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 6
-</t>
-        </is>
+      <c r="G35" s="12" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13 72
-</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>16.8</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr"/>
       <c r="N35" s="3" t="n">
-        <v>25.8</v>
+        <v>243.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="S35" s="3" t="n">
+      <c r="S35" s="8" t="n">
         <v>29</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>275.4</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>9.4</v>
@@ -3517,13 +3359,13 @@
         <v>24.4</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>24.2</v>
+        <v>29.3</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>1.3</v>
+        <v>14.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3539,41 +3381,31 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>117.2</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F36" s="15" t="n">
-        <v>43.9</v>
+        <v>1117.2</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>24.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222725
-1142811042
-</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 6
-</t>
-        </is>
+        <v>72.5</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>0.6</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13 72
-</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>16.3</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>21.9</v>
@@ -3581,14 +3413,14 @@
       <c r="M36" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>20.9</v>
+      <c r="N36" s="8" t="n">
+        <v>25.8</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>28</v>
+        <v>198</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>6.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>21.5</v>
@@ -3600,25 +3432,25 @@
         <v>24.3</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>94.8</v>
+        <v>194.8</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="V36" s="12" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="W36" s="3" t="n">
+      <c r="V36" s="8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W36" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="X36" s="3" t="n">
+      <c r="X36" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>4.8</v>
+        <v>94.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3634,79 +3466,58 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="D37" s="13" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="E37" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="F37" s="13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>42.9</v>
+        <v>826.4</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>143</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="G37" s="17" t="n">
+        <v>14.3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>92.40000000000001</v>
-      </c>
+        <v>15.8</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr"/>
       <c r="K37" s="3" t="n">
-        <v>17.3</v>
+        <v>117.9</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>1034.4</v>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">777
-22
-7
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="O37" s="3" t="n">
-        <v>425</v>
-      </c>
+        <v>103.4</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr"/>
+      <c r="O37" s="3" t="inlineStr"/>
       <c r="P37" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>1334.1</v>
-      </c>
-      <c r="R37" s="3" t="n">
-        <v>117.9</v>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v>86.3</v>
-      </c>
+        <v>133.1</v>
+      </c>
+      <c r="R37" s="3" t="inlineStr"/>
+      <c r="S37" s="3" t="inlineStr"/>
       <c r="T37" s="3" t="n">
         <v>393.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="V37" s="3" t="n">
-        <v>124.1</v>
-      </c>
-      <c r="W37" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="X37" s="3" t="n"/>
+        <v>140.4</v>
+      </c>
+      <c r="V37" s="3" t="inlineStr"/>
+      <c r="W37" s="3" t="inlineStr"/>
+      <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>416</v>
+        <v>1416</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>0.7</v>
+        <v>128</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3722,71 +3533,69 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>165.3</v>
-      </c>
-      <c r="D38" s="10" t="n">
+        <v>163.3</v>
+      </c>
+      <c r="D38" s="12" t="n">
         <v>28.6</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="F38" s="12" t="n">
         <v>24.3</v>
       </c>
-      <c r="G38" s="10" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>18.6</v>
+      <c r="G38" s="12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>68.59999999999999</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K38" s="3" t="n"/>
+        <v>12.2</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>61.3</v>
+        <v>20</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q38" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q38" s="8" t="n">
         <v>26.6</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="S38" s="3" t="n">
-        <v>73.5</v>
+      <c r="S38" s="8" t="n">
+        <v>927.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="V38" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="X38" s="3" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v>811.1</v>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X38" s="8" t="n">
         <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>8324.799999999999</v>
+        <v>1839.2</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>5.6</v>
@@ -3805,78 +3614,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="D39" s="15" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="F39" s="10" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="D39" s="17" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="F39" s="3" t="n">
         <v>25</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="H39" s="3" t="n">
-        <v>18</v>
+      <c r="H39" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7 29
-15
-</t>
-        </is>
+        <v>93.5</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>19.5</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>10.6</v>
+        <v>19.2</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>22.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>99</v>
+        <v>1100</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>10.1</v>
+        <v>10</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>130.7</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>89.3</v>
+        <v>29.3</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>666.1</v>
-      </c>
-      <c r="U39" s="12" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>61.2</v>
+        <v>166.5</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v>27.8</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>22.6</v>
+        <v>23.9</v>
+      </c>
+      <c r="X39" s="8" t="n">
+        <v>27.2</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>2.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>6.1</v>
+        <v>106.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3892,71 +3699,73 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="D40" s="15" t="n">
-        <v>44.8</v>
+        <v>278.1</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>30.8</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="F40" s="10" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>25.7</v>
       </c>
-      <c r="G40" s="3" t="n">
+      <c r="G40" s="12" t="n">
         <v>10.2</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K40" s="3" t="n"/>
+        <v>3.1</v>
+      </c>
+      <c r="K40" s="8" t="n">
+        <v>0.4</v>
+      </c>
       <c r="L40" s="3" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="N40" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="N40" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>990.6</v>
+        <v>99</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="R40" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q40" s="8" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="R40" s="8" t="n">
         <v>25.3</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>165.4</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="8" t="n">
         <v>28</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X40" s="3" t="n">
+      <c r="X40" s="8" t="n">
         <v>27.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>0.1</v>
+        <v>72.2</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>10.4</v>
@@ -3977,78 +3786,74 @@
       <c r="C41" s="3" t="n">
         <v>242.6</v>
       </c>
-      <c r="D41" s="15" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="F41" s="10" t="n">
+      <c r="D41" s="12" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>25.2</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="I41" s="3" t="n">
-        <v>1.5</v>
+      <c r="I41" s="8" t="n">
+        <v>18.5</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">442
-111
-</t>
-        </is>
+        <v>16.9</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98.8</v>
+        <v>193.8</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q41" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="R41" s="3" t="n">
+      <c r="Q41" s="8" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="R41" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="S41" s="3" t="n">
+      <c r="S41" s="8" t="n">
         <v>28.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="U41" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>22.1</v>
+        <v>720.5</v>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v>27.1</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>22.1</v>
+        <v>645.1</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>24.4</v>
+        <v>1841.1</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>6.7</v>
+        <v>16.7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4066,74 +3871,74 @@
       <c r="C42" s="3" t="n">
         <v>288.6</v>
       </c>
-      <c r="D42" s="10" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="F42" s="10" t="n">
+      <c r="D42" s="12" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>25.6</v>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="G42" s="12" t="n">
         <v>10.5</v>
       </c>
-      <c r="H42" s="3" t="n">
-        <v>18.6</v>
+      <c r="H42" s="8" t="n">
+        <v>188.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>1.5</v>
+        <v>16.6</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
+      </c>
+      <c r="K42" s="8" t="n">
+        <v>0.4</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="N42" s="12" t="n">
-        <v>52.8</v>
+        <v>21.2</v>
+      </c>
+      <c r="M42" s="8" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>25.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>10618.2</v>
+        <v>1600</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q42" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="S42" s="3" t="n">
+      <c r="S42" s="8" t="n">
         <v>27.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>0.4</v>
+        <v>162</v>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v>207.1</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X42" s="3" t="n">
-        <v>29.3</v>
+      <c r="X42" s="8" t="n">
+        <v>239.3</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>0.2</v>
+        <v>181.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>6.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4149,74 +3954,74 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>311.6</v>
-      </c>
-      <c r="D43" s="10" t="n">
+        <v>2311.6</v>
+      </c>
+      <c r="D43" s="12" t="n">
         <v>30.8</v>
       </c>
-      <c r="E43" s="10" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="F43" s="10" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G43" s="3" t="n">
+      <c r="E43" s="12" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G43" s="12" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H43" s="3" t="n">
+      <c r="H43" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="I43" s="3" t="n">
-        <v>1.6</v>
-      </c>
+      <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.2</v>
+        <v>3.9</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n">
+      <c r="M43" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="N43" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q43" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q43" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="S43" s="3" t="n">
+      <c r="R43" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="S43" s="8" t="n">
         <v>24</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>726</v>
+        <v>17</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>24</v>
+        <v>24.8</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>2.9</v>
+        <v>22</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>35.4</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>84.3</v>
+        <v>184.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>4.6</v>
+        <v>14.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4231,80 +4036,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
-        <v>311.6</v>
-      </c>
-      <c r="D44" s="15" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="F44" s="10" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G44" s="15" t="n">
-        <v>546.5</v>
-      </c>
-      <c r="H44" s="12" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42424
-211
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-111562
-</t>
-        </is>
-      </c>
-      <c r="N44" s="12" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="O44" s="3" t="n"/>
-      <c r="P44" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q44" s="12" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="R44" s="12" t="n">
-        <v>373.3</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="T44" s="3" t="n">
-        <v>726</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="X44" s="12" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>3242.3</v>
-      </c>
-      <c r="Z44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4319,72 +4074,54 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1453.4</v>
-      </c>
-      <c r="D45" s="13" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E45" s="13" t="n">
-        <v>779.7</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>153</v>
-      </c>
+        <v>1722.7</v>
+      </c>
+      <c r="D45" s="16" t="inlineStr"/>
+      <c r="E45" s="16" t="inlineStr"/>
+      <c r="F45" s="16" t="inlineStr"/>
       <c r="G45" s="3" t="n">
-        <v>50.6</v>
+        <v>6.1</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>93.59999999999999</v>
+        <v>293.6</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n">
-        <v>113.8</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>164.9</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="L45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>494.2</v>
-      </c>
-      <c r="P45" s="3" t="n"/>
+        <v>191.8</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Q45" s="3" t="n">
-        <v>146.3</v>
-      </c>
-      <c r="R45" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>78.09999999999999</v>
-      </c>
+        <v>146.2</v>
+      </c>
+      <c r="R45" s="3" t="inlineStr"/>
+      <c r="S45" s="3" t="inlineStr"/>
       <c r="T45" s="3" t="n">
         <v>341.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="V45" s="3" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="W45" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X45" s="3" t="n">
-        <v>27.6</v>
-      </c>
+        <v>1668</v>
+      </c>
+      <c r="V45" s="3" t="inlineStr"/>
+      <c r="W45" s="3" t="inlineStr"/>
+      <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>3242.3</v>
+        <v>992.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>38.3</v>
+        <v>198.5</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4402,74 +4139,72 @@
       <c r="C46" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D46" s="10" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E46" s="10" t="n">
+      <c r="D46" s="12" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E46" s="12" t="n">
         <v>20.5</v>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G46" s="10" t="n">
+      <c r="F46" s="12" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G46" s="12" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="3" t="n">
+      <c r="H46" s="8" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I46" s="3" t="n">
         <v>18.7</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="L46" s="12" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>10.5</v>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>20.6</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>4.4</v>
+        <v>24.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>198.4</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q46" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q46" s="8" t="n">
         <v>29.3</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="S46" s="12" t="n">
-        <v>77.2</v>
+        <v>645.1</v>
+      </c>
+      <c r="S46" s="8" t="n">
+        <v>27.7</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="U46" s="12" t="n">
-        <v>32.4</v>
+        <v>168.3</v>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v>292.2</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>0.1</v>
+        <v>26.8</v>
+      </c>
+      <c r="W46" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X46" s="8" t="n">
+        <v>22.6</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>8.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>2.7</v>
+        <v>7.8</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -47,12 +47,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -61,6 +55,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -149,28 +155,28 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -789,61 +795,59 @@
       <c r="C4" s="3" t="n">
         <v>351.3</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="11" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="11" t="n">
         <v>22.7</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="11" t="n">
         <v>28.1</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="11" t="n">
         <v>10.8</v>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="H4" s="3" t="n">
         <v>21</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>21.6</v>
+        <v>2.6</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="3" t="n">
         <v>22.7</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>27.4</v>
+        <v>28.4</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>97.5</v>
       </c>
-      <c r="P4" s="8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q4" s="8" t="n">
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="R4" s="8" t="n">
+      <c r="R4" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="S4" s="8" t="n">
-        <v>1281.1</v>
+      <c r="S4" s="3" t="n">
+        <v>28.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>156.1</v>
-      </c>
-      <c r="U4" s="8" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="U4" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="V4" s="8" t="n">
+      <c r="V4" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="W4" s="3" t="n">
@@ -855,9 +859,7 @@
       <c r="Y4" s="3" t="n">
         <v>174.3</v>
       </c>
-      <c r="Z4" s="3" t="n">
-        <v>110</v>
-      </c>
+      <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -874,26 +876,26 @@
       <c r="C5" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="11" t="n">
         <v>20.8</v>
       </c>
-      <c r="F5" s="12" t="n">
+      <c r="F5" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="11" t="n">
         <v>10.3</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>3.1</v>
+        <v>31.1</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>1.9</v>
@@ -901,29 +903,29 @@
       <c r="L5" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.5</v>
+        <v>25.4</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q5" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>26</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S5" s="8" t="n">
+      <c r="S5" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>7.4</v>
@@ -931,17 +933,17 @@
       <c r="V5" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="X5" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>192</v>
+        <v>92</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>2.1</v>
+        <v>12.1</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -957,53 +959,51 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12368</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E6" s="12" t="n">
+        <v>2368</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E6" s="11" t="n">
         <v>21.1</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="11" t="n">
         <v>26.3</v>
       </c>
-      <c r="G6" s="17" t="n">
-        <v>41</v>
+      <c r="G6" s="3" t="n">
+        <v>20.3</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L6" s="8" t="n">
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="N6" s="8" t="n">
+      <c r="N6" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="Q6" s="8" t="n">
+        <v>92</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="R6" s="8" t="n">
+      <c r="R6" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S6" s="3" t="n">
-        <v>41.3</v>
+      <c r="S6" s="8" t="n">
+        <v>75.3</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>99.59999999999999</v>
@@ -1014,17 +1014,17 @@
       <c r="V6" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="X6" s="8" t="n">
+      <c r="X6" s="3" t="n">
         <v>29</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>175.4</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>9.4</v>
+        <v>19.8</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1040,31 +1040,31 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>418.2</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="F7" s="12" t="n">
+        <v>1418.2</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="F7" s="11" t="n">
         <v>26.7</v>
       </c>
-      <c r="G7" s="12" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>944.4</v>
+      <c r="G7" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>89.40000000000001</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>20.3</v>
+        <v>2.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>11.3</v>
+        <v>12.5</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>21.1</v>
@@ -1073,43 +1073,43 @@
         <v>20.9</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>46.1</v>
+        <v>24.6</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1980.8</v>
+        <v>98</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>311.9</v>
-      </c>
-      <c r="R7" s="8" t="n">
-        <v>25.3</v>
+        <v>31.9</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>159.5</v>
-      </c>
-      <c r="U7" s="8" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="U7" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W7" s="8" t="n">
+      <c r="W7" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="X7" s="8" t="n">
         <v>28.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>73.2</v>
+        <v>173.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>10.5</v>
+        <v>110.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1125,18 +1125,18 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>19368</v>
-      </c>
-      <c r="D8" s="12" t="n">
+        <v>14268</v>
+      </c>
+      <c r="D8" s="11" t="n">
         <v>33.2</v>
       </c>
-      <c r="E8" s="12" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="F8" s="12" t="n">
+      <c r="E8" s="11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="F8" s="11" t="n">
         <v>27.5</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="11" t="n">
         <v>11.5</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1146,39 +1146,39 @@
         <v>3.5</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>15.8</v>
+        <v>5.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L8" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L8" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="M8" s="8" t="n">
-        <v>41.7</v>
+      <c r="M8" s="3" t="n">
+        <v>21.7</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>196.5</v>
-      </c>
-      <c r="P8" s="8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q8" s="8" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>33.3</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="S8" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>194.8</v>
-      </c>
-      <c r="U8" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U8" s="3" t="n">
         <v>23</v>
       </c>
       <c r="V8" s="3" t="n">
@@ -1187,7 +1187,7 @@
       <c r="W8" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="X8" s="3" t="n">
+      <c r="X8" s="8" t="n">
         <v>28.2</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1210,19 +1210,21 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>17183.6</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>161.5</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>107.5</v>
-      </c>
-      <c r="F9" s="12" t="n">
+        <v>1183</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="F9" s="11" t="n">
         <v>134.5</v>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="n">
+        <v>8081.1</v>
+      </c>
       <c r="I9" s="3" t="n">
         <v>112</v>
       </c>
@@ -1233,29 +1235,35 @@
         <v>2</v>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="n">
+        <v>108012.8</v>
+      </c>
       <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="n">
-        <v>487</v>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
+        <v>1487</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="n">
+        <v>256.6</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>124.4</v>
+      </c>
       <c r="S9" s="3" t="n">
-        <v>1371.5</v>
+        <v>1137.5</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>908</v>
+        <v>1308</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>190.1</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
-      <c r="W9" s="3" t="inlineStr"/>
+      <c r="W9" s="3" t="n">
+        <v>200139.5</v>
+      </c>
       <c r="X9" s="3" t="n">
-        <v>1032.5</v>
+        <v>1139.5</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>1389.1</v>
@@ -1277,32 +1285,30 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2356.7</v>
-      </c>
-      <c r="D10" s="12" t="n">
+        <v>19856.7</v>
+      </c>
+      <c r="D10" s="11" t="n">
         <v>32.3</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="11" t="n">
         <v>21.5</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="11" t="n">
         <v>26.9</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="11" t="n">
         <v>10.8</v>
       </c>
-      <c r="H10" s="8" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="H10" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="n">
-        <v>4.2</v>
+        <v>42.8</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
-        <v>21.9</v>
+        <v>22.9</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>21.6</v>
@@ -1311,30 +1317,30 @@
         <v>25.6</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>197.4</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q10" s="8" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q10" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="R10" s="8" t="n">
+      <c r="R10" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S10" s="8" t="n">
+      <c r="S10" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>161.6</v>
-      </c>
-      <c r="U10" s="3" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="U10" s="8" t="n">
         <v>18</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X10" s="8" t="n">
@@ -1360,34 +1366,34 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>453.1</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>26.6</v>
+        <v>4.3</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>93.92999999999999</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>26.5</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="H11" s="8" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H11" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>14.1</v>
+      <c r="I11" s="8" t="n">
+        <v>12.1</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>71.09999999999999</v>
+        <v>47</v>
       </c>
       <c r="K11" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="L11" s="3" t="n">
-        <v>20.6</v>
+      <c r="L11" s="8" t="n">
+        <v>1.6</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>20.5</v>
@@ -1396,10 +1402,10 @@
         <v>24</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>33.2</v>
@@ -1407,8 +1413,8 @@
       <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="S11" s="8" t="n">
-        <v>28.5</v>
+      <c r="S11" s="3" t="n">
+        <v>28.6</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>156.3</v>
@@ -1416,17 +1422,17 @@
       <c r="U11" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="V11" s="8" t="n">
+      <c r="V11" s="3" t="n">
         <v>29.5</v>
       </c>
-      <c r="W11" s="8" t="n">
-        <v>655.1</v>
+      <c r="W11" s="3" t="n">
+        <v>25.1</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>29</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>170.4</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>12.2</v>
@@ -1445,43 +1451,43 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>141824</v>
-      </c>
-      <c r="D12" s="12" t="n">
+        <v>1418.2</v>
+      </c>
+      <c r="D12" s="11" t="n">
         <v>32.8</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="11" t="n">
         <v>20.2</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="11" t="n">
         <v>12.6</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>13</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="L12" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L12" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="M12" s="8" t="n">
+      <c r="M12" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>220.3</v>
+        <v>23.3</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.7</v>
@@ -1496,22 +1502,22 @@
         <v>28.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>1958</v>
-      </c>
-      <c r="U12" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="U12" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="V12" s="8" t="n">
+      <c r="V12" s="3" t="n">
         <v>29.6</v>
       </c>
-      <c r="W12" s="3" t="n">
-        <v>25.6</v>
+      <c r="W12" s="8" t="n">
+        <v>5.6</v>
       </c>
       <c r="X12" s="8" t="n">
         <v>30.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>713.2</v>
+        <v>1713.2</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>11.1</v>
@@ -1530,18 +1536,18 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1230.1</v>
-      </c>
-      <c r="D13" s="12" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="D13" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="E13" s="12" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F13" s="12" t="n">
+      <c r="E13" s="11" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F13" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" s="11" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="H13" s="8" t="n">
@@ -1550,51 +1556,51 @@
       <c r="I13" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="J13" s="8" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="K13" s="8" t="n">
+      <c r="J13" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K13" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="L13" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="3" t="n">
         <v>21</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>24.7</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="8" t="n">
-        <v>229.1</v>
-      </c>
-      <c r="R13" s="8" t="n">
+      <c r="Q13" s="3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="R13" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="S13" s="8" t="n">
+      <c r="S13" s="3" t="n">
         <v>27.3</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>167.9</v>
-      </c>
-      <c r="U13" s="8" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="U13" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="V13" s="8" t="n">
+      <c r="V13" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X13" s="8" t="n">
+      <c r="X13" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>80.8</v>
+        <v>180.8</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>16.6</v>
@@ -1613,19 +1619,19 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1821.4</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="E14" s="12" t="n">
+        <v>121.4</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E14" s="11" t="n">
         <v>19.4</v>
       </c>
-      <c r="F14" s="12" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>80.09999999999999</v>
+      <c r="F14" s="11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>8.1</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>17.8</v>
@@ -1634,31 +1640,31 @@
         <v>0.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>18.6</v>
+        <v>11.6</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>41.1</v>
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N14" s="8" t="n">
+      <c r="N14" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q14" s="8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q14" s="3" t="n">
         <v>27.3</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>24.8</v>
+        <v>24.2</v>
       </c>
       <c r="S14" s="3" t="n">
         <v>28.2</v>
@@ -1667,7 +1673,7 @@
         <v>77.8</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>18.1</v>
+        <v>8.1</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>26</v>
@@ -1675,14 +1681,14 @@
       <c r="W14" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="X14" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>851.1</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1698,76 +1704,76 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>340.8</v>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F15" s="12" t="n">
+        <v>240.8</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F15" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="G15" s="11" t="n">
         <v>12.1</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>94.5</v>
+        <v>2.5</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K15" s="8" t="n">
-        <v>8</v>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="M15" s="8" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="N15" s="8" t="n">
+      <c r="M15" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="N15" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="8" t="n">
+      <c r="Q15" s="3" t="n">
         <v>30</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="S15" s="8" t="n">
+      <c r="S15" s="3" t="n">
         <v>30</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="U15" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="W15" s="8" t="n">
+      <c r="U15" s="8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="W15" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="X15" s="8" t="n">
+      <c r="X15" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>16.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1782,59 +1788,67 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="12" t="n">
-        <v>154</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="F16" s="12" t="n">
+      <c r="C16" s="3" t="n">
+        <v>1530.8</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>154.2</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="F16" s="11" t="n">
         <v>126.8</v>
       </c>
-      <c r="G16" s="17" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>192.1</v>
-      </c>
+      <c r="G16" s="3" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr"/>
       <c r="I16" s="3" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>186.4</v>
+        <v>162.4</v>
       </c>
       <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="n">
+        <v>1919</v>
+      </c>
       <c r="N16" s="3" t="inlineStr"/>
       <c r="O16" s="3" t="n">
         <v>1490</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>152.4</v>
       </c>
       <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="n">
+        <v>127331</v>
+      </c>
       <c r="T16" s="3" t="n">
-        <v>1331</v>
+        <v>331</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>176.3</v>
+        <v>178</v>
       </c>
       <c r="V16" s="3" t="inlineStr"/>
-      <c r="W16" s="3" t="inlineStr"/>
-      <c r="X16" s="3" t="inlineStr"/>
+      <c r="W16" s="3" t="n">
+        <v>20419</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>11480</v>
+      </c>
       <c r="Y16" s="3" t="n">
-        <v>1386.1</v>
+        <v>11386.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>42.3</v>
+        <v>142.3</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1852,70 +1866,70 @@
       <c r="C17" s="3" t="n">
         <v>306.2</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="17" t="n">
         <v>30.8</v>
       </c>
-      <c r="E17" s="12" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F17" s="12" t="n">
+      <c r="E17" s="15" t="inlineStr"/>
+      <c r="F17" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="G17" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="I17" s="3" t="n">
-        <v>23.5</v>
+      <c r="I17" s="8" t="n">
+        <v>22.9</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
-        <v>20.6</v>
+      <c r="L17" s="8" t="n">
+        <v>60.5</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>23.8</v>
+        <v>21.4</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>90.5</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S17" s="8" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="S17" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>166.2</v>
       </c>
-      <c r="U17" s="3" t="n">
-        <v>15.3</v>
+      <c r="U17" s="8" t="n">
+        <v>152.3</v>
       </c>
       <c r="V17" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W17" s="3" t="inlineStr"/>
-      <c r="X17" s="3" t="n">
+      <c r="W17" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X17" s="8" t="n">
         <v>28</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>1717.2</v>
+        <v>1741.2</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>53.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1931,76 +1945,76 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="D18" s="12" t="n">
+        <v>3321.1</v>
+      </c>
+      <c r="D18" s="11" t="n">
         <v>32.2</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="11" t="n">
         <v>19.2</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="F18" s="11" t="n">
         <v>25.7</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G18" s="11" t="n">
         <v>13</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>67.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>20.4</v>
+        <v>12.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K18" s="8" t="n">
-        <v>8.4</v>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <v>89.40000000000001</v>
+      <c r="M18" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q18" s="8" t="n">
+      <c r="Q18" s="3" t="n">
         <v>32.2</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="R18" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="S18" s="8" t="n">
+      <c r="S18" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>158</v>
       </c>
-      <c r="U18" s="8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V18" s="8" t="n">
+      <c r="U18" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="V18" s="3" t="n">
         <v>28.3</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>229.8</v>
+        <v>29.8</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>177.6</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>8.6</v>
+        <v>18.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2016,58 +2030,58 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1326.2</v>
-      </c>
-      <c r="D19" s="12" t="n">
+        <v>326.2</v>
+      </c>
+      <c r="D19" s="11" t="n">
         <v>32.1</v>
       </c>
-      <c r="E19" s="12" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="G19" s="12" t="n">
+      <c r="E19" s="11" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="G19" s="11" t="n">
         <v>11.7</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="L19" s="8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="N19" s="8" t="n">
+      <c r="N19" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q19" s="8" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="R19" s="8" t="n">
+      <c r="Q19" s="3" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="R19" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="S19" s="8" t="n">
+      <c r="S19" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>160.5</v>
+        <v>60.5</v>
       </c>
       <c r="U19" s="3" t="n">
         <v>18.4</v>
@@ -2076,7 +2090,7 @@
         <v>25.7</v>
       </c>
       <c r="W19" s="8" t="n">
-        <v>24.2</v>
+        <v>22.2</v>
       </c>
       <c r="X19" s="8" t="n">
         <v>29.2</v>
@@ -2085,7 +2099,7 @@
         <v>188.5</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>3.8</v>
+        <v>18.8</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2103,29 +2117,29 @@
       <c r="C20" s="3" t="n">
         <v>1299</v>
       </c>
-      <c r="D20" s="17" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="F20" s="8" t="n">
+      <c r="D20" s="11" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F20" s="11" t="n">
         <v>24.7</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="11" t="n">
         <v>10</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>31.5</v>
+        <v>3.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="L20" s="8" t="n">
         <v>19.8</v>
@@ -2134,38 +2148,40 @@
         <v>19.7</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="O20" s="3" t="inlineStr"/>
+        <v>22.8</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>199</v>
+      </c>
       <c r="P20" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Q20" s="8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q20" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="R20" s="8" t="n">
-        <v>238.4</v>
+      <c r="R20" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>171.6</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V20" s="8" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="V20" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="W20" s="8" t="n">
+      <c r="W20" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="X20" s="8" t="n">
+      <c r="X20" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>5.4</v>
@@ -2184,27 +2200,27 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1357.5</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E21" s="12" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E21" s="11" t="n">
         <v>18.1</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="F21" s="11" t="n">
         <v>24.1</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="G21" s="11" t="n">
         <v>12.1</v>
       </c>
-      <c r="H21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="n">
+        <v>16.4</v>
+      </c>
       <c r="I21" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>3.8</v>
-      </c>
+        <v>12.2</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="n">
         <v>10</v>
       </c>
@@ -2212,21 +2228,21 @@
         <v>18.9</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N21" s="8" t="n">
-        <v>12.8</v>
+        <v>88.90000000000001</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>21.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1001</v>
-      </c>
-      <c r="P21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="8" t="n">
+      <c r="R21" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2236,12 +2252,12 @@
         <v>163.1</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="V21" s="3" t="n">
+        <v>452.6</v>
+      </c>
+      <c r="V21" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W21" s="8" t="n">
+      <c r="W21" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="X21" s="8" t="n">
@@ -2251,7 +2267,7 @@
         <v>184.1</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>5.4</v>
+        <v>15.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2267,32 +2283,32 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1294.9</v>
-      </c>
-      <c r="D22" s="17" t="n">
-        <v>531.2</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F22" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>12.8</v>
+        <v>2994.3</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>25.8</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>17.4</v>
+        <v>179.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>16.9</v>
+        <v>1.9</v>
       </c>
       <c r="J22" s="3" t="inlineStr"/>
       <c r="K22" s="3" t="n">
-        <v>10.1</v>
+        <v>0.1</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>69.09999999999999</v>
+        <v>19.1</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>19.1</v>
@@ -2301,12 +2317,12 @@
         <v>22.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P22" s="8" t="n">
+        <v>108</v>
+      </c>
+      <c r="P22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="8" t="n">
+      <c r="Q22" s="3" t="n">
         <v>31</v>
       </c>
       <c r="R22" s="3" t="n">
@@ -2321,20 +2337,20 @@
       <c r="U22" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="W22" s="8" t="n">
+      <c r="W22" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>216.5</v>
+        <v>26.5</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>88.8</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>3.3</v>
+        <v>13.3</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2349,15 +2365,23 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="16" t="inlineStr"/>
-      <c r="E23" s="16" t="inlineStr"/>
-      <c r="F23" s="16" t="inlineStr"/>
-      <c r="G23" s="3" t="n">
-        <v>59.2</v>
+      <c r="C23" s="3" t="n">
+        <v>16101.1</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>156</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>2285.9</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>88.2</v>
+        <v>188.4</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>10.4</v>
@@ -2367,33 +2391,39 @@
       </c>
       <c r="K23" s="3" t="inlineStr"/>
       <c r="L23" s="3" t="n">
-        <v>198.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="n">
+        <v>133494</v>
+      </c>
       <c r="O23" s="3" t="n">
-        <v>494</v>
+        <v>1494</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
-        <v>1252.9</v>
+        <v>252.9</v>
       </c>
       <c r="R23" s="3" t="inlineStr"/>
-      <c r="S23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="n">
+        <v>32732</v>
+      </c>
       <c r="T23" s="3" t="n">
         <v>1320</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>179.6</v>
+        <v>7896.1</v>
       </c>
       <c r="V23" s="3" t="inlineStr"/>
-      <c r="W23" s="3" t="inlineStr"/>
+      <c r="W23" s="3" t="n">
+        <v>4220.6</v>
+      </c>
       <c r="X23" s="3" t="inlineStr"/>
       <c r="Y23" s="3" t="n">
-        <v>422</v>
+        <v>1422</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>26.5</v>
+        <v>126.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2409,54 +2439,56 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>322</v>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E24" s="12" t="n">
+        <v>2822</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E24" s="11" t="n">
         <v>19.3</v>
       </c>
-      <c r="F24" s="12" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="G24" s="12" t="n">
+      <c r="F24" s="11" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="G24" s="11" t="n">
         <v>11.9</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2.1</v>
+        <v>21.1</v>
       </c>
       <c r="J24" s="3" t="inlineStr"/>
-      <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="8" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="M24" s="8" t="n">
+      <c r="K24" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="M24" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.8</v>
+        <v>22.7</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>988.1</v>
+        <v>98.8</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>10.3</v>
+        <v>5.3</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>20</v>
       </c>
       <c r="R24" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="S24" s="8" t="n">
+      <c r="S24" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>164</v>
+        <v>64</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>15.9</v>
@@ -2464,17 +2496,17 @@
       <c r="V24" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="W24" s="8" t="n">
+      <c r="W24" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X24" s="8" t="n">
+      <c r="X24" s="3" t="n">
         <v>28.1</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>184.4</v>
+        <v>194.4</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>55.3</v>
+        <v>5.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2490,44 +2522,46 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>177.8</v>
-      </c>
-      <c r="D25" s="3" t="n">
+        <v>1177.8</v>
+      </c>
+      <c r="D25" s="11" t="n">
         <v>30.1</v>
       </c>
-      <c r="E25" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F25" s="17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>10.8</v>
+      <c r="E25" s="11" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>10.3</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="J25" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>17.6</v>
+        <v>5.6</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M25" s="3" t="n">
-        <v>194.4</v>
-      </c>
-      <c r="N25" s="8" t="n">
+      <c r="M25" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="N25" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>22.9</v>
@@ -2535,29 +2569,29 @@
       <c r="R25" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="S25" s="8" t="n">
+      <c r="S25" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>93.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="V25" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="W25" s="8" t="n">
+      <c r="W25" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>95.2</v>
+        <v>1595.2</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2573,18 +2607,18 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2345</v>
-      </c>
-      <c r="D26" s="12" t="n">
+        <v>2245</v>
+      </c>
+      <c r="D26" s="11" t="n">
         <v>31.7</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="11" t="n">
         <v>20.5</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F26" s="11" t="n">
         <v>26.1</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="G26" s="11" t="n">
         <v>11.2</v>
       </c>
       <c r="H26" s="8" t="n">
@@ -2595,7 +2629,7 @@
         <v>14.4</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>20.6</v>
@@ -2604,10 +2638,10 @@
         <v>20.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>23.8</v>
+        <v>958.6</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0.4</v>
@@ -2616,7 +2650,7 @@
         <v>31.4</v>
       </c>
       <c r="R26" s="8" t="n">
-        <v>24.1</v>
+        <v>49.1</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>25.3</v>
@@ -2627,20 +2661,20 @@
       <c r="U26" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="V26" s="8" t="n">
+      <c r="V26" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="W26" s="8" t="n">
+      <c r="W26" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>62.1</v>
+        <v>26.8</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>174.3</v>
+        <v>14.3</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2656,29 +2690,29 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2418.2</v>
-      </c>
-      <c r="D27" s="8" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F27" s="17" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="G27" s="3" t="n">
+        <v>12418.2</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="G27" s="11" t="n">
         <v>13.7</v>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="H27" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>19.6</v>
@@ -2690,22 +2724,22 @@
         <v>22.6</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>4.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>32.9</v>
       </c>
-      <c r="R27" s="8" t="n">
+      <c r="R27" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S27" s="8" t="n">
+      <c r="S27" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>153</v>
+        <v>53</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>23.4</v>
@@ -2713,11 +2747,11 @@
       <c r="V27" s="3" t="n">
         <v>29.3</v>
       </c>
-      <c r="W27" s="8" t="n">
-        <v>95.5</v>
+      <c r="W27" s="3" t="n">
+        <v>65.5</v>
       </c>
       <c r="X27" s="8" t="n">
-        <v>30.2</v>
+        <v>808.2</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>174.2</v>
@@ -2741,74 +2775,74 @@
       <c r="C28" s="3" t="n">
         <v>282.3</v>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="D28" s="11" t="n">
         <v>32.6</v>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="F28" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="G28" s="11" t="n">
         <v>12.8</v>
       </c>
       <c r="H28" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>12.6</v>
+        <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>49.9</v>
+        <v>29.9</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>33.4</v>
+        <v>23.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q28" s="8" t="n">
+      <c r="Q28" s="3" t="n">
         <v>29.7</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="S28" s="8" t="n">
+      <c r="S28" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>169.4</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="V28" s="8" t="n">
-        <v>224.4</v>
+      <c r="V28" s="3" t="n">
+        <v>24.4</v>
       </c>
       <c r="W28" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="X28" s="8" t="n">
-        <v>260.3</v>
+        <v>26.9</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>186</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>14.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2824,48 +2858,46 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>120.2</v>
-      </c>
-      <c r="D29" s="12" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E29" s="12" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F29" s="12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F29" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="G29" s="12" t="n">
-        <v>8.9</v>
+      <c r="G29" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="K29" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="M29" s="8" t="n">
+      <c r="M29" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="N29" s="8" t="n">
         <v>25.4</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>196.5</v>
+        <v>96.5</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q29" s="8" t="n">
+      <c r="Q29" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R29" s="8" t="n">
@@ -2875,15 +2907,15 @@
         <v>28.8</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>173.7</v>
+        <v>179.7</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="V29" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="W29" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="W29" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="X29" s="8" t="n">
@@ -2893,7 +2925,7 @@
         <v>181.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>5.8</v>
+        <v>15.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2909,50 +2941,64 @@
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="16" t="inlineStr"/>
-      <c r="E30" s="16" t="inlineStr"/>
-      <c r="F30" s="16" t="inlineStr"/>
-      <c r="G30" s="17" t="n">
-        <v>50.7</v>
+      <c r="D30" s="11" t="n">
+        <v>156.4</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>56.9</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>192.2</v>
+        <v>92.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>9.9</v>
+        <v>19.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>16.7</v>
+        <v>11.9</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>123.7</v>
       </c>
       <c r="L30" s="3" t="inlineStr"/>
-      <c r="M30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="n">
+        <v>101111.2</v>
+      </c>
       <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>1489.5</v>
+        <v>8482.799999999999</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>121</v>
+        <v>12.3</v>
       </c>
       <c r="Q30" s="3" t="inlineStr"/>
-      <c r="R30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="n">
+        <v>22013.5</v>
+      </c>
       <c r="S30" s="3" t="inlineStr"/>
       <c r="T30" s="3" t="n">
-        <v>1344.5</v>
+        <v>2344.5</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>168.8</v>
       </c>
-      <c r="V30" s="3" t="inlineStr"/>
+      <c r="V30" s="3" t="n">
+        <v>127.4</v>
+      </c>
       <c r="W30" s="3" t="inlineStr"/>
-      <c r="X30" s="3" t="inlineStr"/>
+      <c r="X30" s="3" t="n">
+        <v>32144.5</v>
+      </c>
       <c r="Y30" s="3" t="n">
-        <v>1411.5</v>
+        <v>12411.5</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>30.9</v>
+        <v>130.9</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -2968,71 +3014,69 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>272.7</v>
-      </c>
-      <c r="D31" s="12" t="n">
+        <v>212.7</v>
+      </c>
+      <c r="D31" s="11" t="n">
         <v>31.3</v>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="F31" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="G31" s="8" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="H31" s="8" t="n">
-        <v>88.40000000000001</v>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>20.1</v>
+        <v>12</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3.4</v>
+        <v>13.4</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="M31" s="8" t="n">
+      <c r="M31" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="N31" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>197.9</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q31" s="8" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="P31" s="8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Q31" s="3" t="n">
         <v>29.1</v>
       </c>
-      <c r="R31" s="8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S31" s="8" t="n">
+      <c r="R31" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="S31" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>168.9</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>255.1</v>
-      </c>
-      <c r="W31" s="8" t="n">
-        <v>23.1</v>
+        <v>68.90000000000001</v>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>831.4</v>
       </c>
       <c r="X31" s="8" t="n">
-        <v>206.7</v>
+        <v>262.8</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>181.3</v>
+        <v>82.3</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>16.2</v>
@@ -3051,25 +3095,25 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1263.5</v>
-      </c>
-      <c r="D32" s="12" t="n">
+        <v>1263.3</v>
+      </c>
+      <c r="D32" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="11" t="n">
         <v>20.4</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="F32" s="11" t="n">
         <v>24.7</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="G32" s="11" t="n">
         <v>8.6</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="H32" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>16.3</v>
+        <v>1.3</v>
       </c>
       <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="3" t="n">
@@ -3078,14 +3122,14 @@
       <c r="L32" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M32" s="8" t="n">
+      <c r="M32" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="N32" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>990.1</v>
+        <v>99</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.2</v>
@@ -3093,26 +3137,26 @@
       <c r="Q32" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="S32" s="8" t="n">
+      <c r="S32" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>169.8</v>
+        <v>69.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="V32" s="8" t="n">
+      <c r="V32" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="W32" s="8" t="n">
-        <v>24.5</v>
+        <v>45.6</v>
       </c>
       <c r="X32" s="8" t="n">
-        <v>29.1</v>
+        <v>298.1</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>181.1</v>
@@ -3134,29 +3178,29 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>144.1</v>
-      </c>
-      <c r="D33" s="12" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="D33" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="F33" s="11" t="n">
         <v>22.9</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>129</v>
+      <c r="G33" s="11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="J33" s="3" t="inlineStr"/>
-      <c r="K33" s="3" t="n">
-        <v>14.5</v>
+      <c r="K33" s="8" t="n">
+        <v>22.5</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>20.8</v>
@@ -3164,42 +3208,44 @@
       <c r="M33" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="N33" s="8" t="n">
+      <c r="N33" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q33" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="S33" s="8" t="n">
+      <c r="S33" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>183.4</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="V33" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="X33" s="8" t="n">
+      <c r="X33" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
         <v>191.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>2.3</v>
+        <v>12.3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3215,22 +3261,22 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1117.8</v>
-      </c>
-      <c r="D34" s="12" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E34" s="12" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F34" s="12" t="n">
+        <v>1117.5</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="F34" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="G34" s="11" t="n">
         <v>11.5</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>167.8</v>
+        <v>17.8</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>11.9</v>
@@ -3252,24 +3298,24 @@
         <v>1100</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="R34" s="8" t="n">
+      <c r="R34" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>70.2</v>
+        <v>20.2</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="V34" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="V34" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="W34" s="8" t="n">
@@ -3298,38 +3344,40 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1284.4</v>
-      </c>
-      <c r="D35" s="12" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E35" s="12" t="n">
+        <v>284.4</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E35" s="11" t="n">
         <v>18.8</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F35" s="11" t="n">
         <v>24.1</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="G35" s="11" t="n">
         <v>10.7</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.5</v>
+        <v>11.5</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>16.8</v>
+        <v>1.8</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="3" t="n">
-        <v>243.1</v>
+        <v>19</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>10.9</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>1100</v>
@@ -3340,14 +3388,14 @@
       <c r="Q35" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R35" s="8" t="n">
+      <c r="R35" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="S35" s="8" t="n">
+      <c r="S35" s="3" t="n">
         <v>29</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>275.4</v>
+        <v>25.4</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>9.4</v>
@@ -3359,10 +3407,10 @@
         <v>24.4</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>29.3</v>
+        <v>25.2</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>85.8</v>
+        <v>185.8</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>14.9</v>
@@ -3383,31 +3431,29 @@
       <c r="C36" s="3" t="n">
         <v>1117.2</v>
       </c>
-      <c r="D36" s="12" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="E36" s="12" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="F36" s="12" t="n">
+      <c r="D36" s="11" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F36" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>72.5</v>
+      <c r="G36" s="11" t="n">
+        <v>7.5</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>11</v>
-      </c>
+        <v>10.6</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr"/>
       <c r="K36" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="L36" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="L36" s="8" t="n">
         <v>21.9</v>
       </c>
       <c r="M36" s="3" t="n">
@@ -3417,7 +3463,7 @@
         <v>25.8</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.4</v>
@@ -3432,11 +3478,9 @@
         <v>24.3</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>194.8</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>1.3</v>
-      </c>
+        <v>94.8</v>
+      </c>
+      <c r="U36" s="3" t="inlineStr"/>
       <c r="V36" s="8" t="n">
         <v>21.4</v>
       </c>
@@ -3447,7 +3491,7 @@
         <v>24.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>94.8</v>
+        <v>194.8</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>1.3</v>
@@ -3466,52 +3510,58 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>826.4</v>
-      </c>
-      <c r="D37" s="12" t="n">
-        <v>143</v>
-      </c>
-      <c r="E37" s="12" t="n">
-        <v>100.2</v>
-      </c>
-      <c r="F37" s="12" t="n">
+        <v>1826.4</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>142.9</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" s="11" t="n">
         <v>121.5</v>
       </c>
-      <c r="G37" s="17" t="n">
-        <v>14.3</v>
+      <c r="G37" s="3" t="n">
+        <v>42.9</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>15.8</v>
+        <v>5.8</v>
       </c>
       <c r="J37" s="3" t="inlineStr"/>
       <c r="K37" s="3" t="n">
-        <v>117.9</v>
+        <v>187.9</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>103.4</v>
+        <v>203.4</v>
       </c>
       <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="n">
+        <v>208092.8</v>
+      </c>
       <c r="O37" s="3" t="inlineStr"/>
       <c r="P37" s="3" t="n">
-        <v>1</v>
+        <v>7104.4</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>133.1</v>
       </c>
       <c r="R37" s="3" t="inlineStr"/>
-      <c r="S37" s="3" t="inlineStr"/>
+      <c r="S37" s="3" t="n">
+        <v>2623.2</v>
+      </c>
       <c r="T37" s="3" t="n">
         <v>393.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>140.4</v>
+        <v>40.4</v>
       </c>
       <c r="V37" s="3" t="inlineStr"/>
-      <c r="W37" s="3" t="inlineStr"/>
+      <c r="W37" s="3" t="n">
+        <v>12712.9</v>
+      </c>
       <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
         <v>1416</v>
@@ -3533,28 +3583,30 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>163.3</v>
-      </c>
-      <c r="D38" s="12" t="n">
+        <v>165.3</v>
+      </c>
+      <c r="D38" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="11" t="n">
         <v>24.3</v>
       </c>
-      <c r="G38" s="12" t="n">
-        <v>8.6</v>
+      <c r="G38" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>68.59999999999999</v>
+        <v>18.6</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>12.2</v>
+        <v>1.2</v>
       </c>
       <c r="J38" s="3" t="inlineStr"/>
-      <c r="K38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="n">
+        <v>420.7</v>
+      </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
@@ -3565,37 +3617,37 @@
         <v>24.2</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="8" t="n">
+      <c r="Q38" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="S38" s="8" t="n">
-        <v>927.3</v>
+      <c r="S38" s="3" t="n">
+        <v>68.3</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>78.7</v>
       </c>
-      <c r="U38" s="8" t="n">
-        <v>811.1</v>
-      </c>
-      <c r="V38" s="8" t="n">
+      <c r="U38" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V38" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W38" s="8" t="n">
+      <c r="W38" s="3" t="n">
         <v>22.5</v>
       </c>
       <c r="X38" s="8" t="n">
         <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>1839.2</v>
+        <v>183.2</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>5.6</v>
@@ -3614,49 +3666,49 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="D39" s="17" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="F39" s="3" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F39" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="G39" s="3" t="n">
+      <c r="G39" s="11" t="n">
         <v>11.4</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>8</v>
+        <v>180.8</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>93.5</v>
+        <v>3.5</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>19.2</v>
+        <v>19.9</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q39" s="8" t="n">
-        <v>130.7</v>
+        <v>2.2</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>30.7</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>25.5</v>
@@ -3665,25 +3717,25 @@
         <v>29.3</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>166.5</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="V39" s="8" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="V39" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="X39" s="8" t="n">
+      <c r="X39" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>72.90000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>106.1</v>
+        <v>10.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3699,63 +3751,61 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>278.1</v>
-      </c>
-      <c r="D40" s="12" t="n">
+        <v>6184.6</v>
+      </c>
+      <c r="D40" s="11" t="n">
         <v>30.8</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="F40" s="11" t="n">
         <v>25.7</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="G40" s="11" t="n">
         <v>10.2</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>19</v>
+        <v>19.6</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K40" s="8" t="n">
-        <v>0.4</v>
+        <v>13.1</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>21</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="N40" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="N40" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P40" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q40" s="8" t="n">
+      <c r="P40" s="3" t="inlineStr"/>
+      <c r="Q40" s="3" t="n">
         <v>30.7</v>
       </c>
-      <c r="R40" s="8" t="n">
+      <c r="R40" s="3" t="n">
         <v>25.3</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>165.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="V40" s="8" t="n">
+      <c r="V40" s="3" t="n">
         <v>28</v>
       </c>
       <c r="W40" s="3" t="n">
@@ -3765,10 +3815,10 @@
         <v>27.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>72.2</v>
+        <v>712.2</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>10.4</v>
+        <v>180.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3784,15 +3834,15 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>242.6</v>
-      </c>
-      <c r="D41" s="12" t="n">
+        <v>242.8</v>
+      </c>
+      <c r="D41" s="11" t="n">
         <v>29.6</v>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="11" t="n">
         <v>20.8</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="F41" s="11" t="n">
         <v>25.2</v>
       </c>
       <c r="G41" s="3" t="n">
@@ -3801,56 +3851,56 @@
       <c r="H41" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="I41" s="8" t="n">
-        <v>18.5</v>
+      <c r="I41" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="L41" s="8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L41" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>20.2</v>
+        <v>26.2</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>193.8</v>
+        <v>93.8</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q41" s="8" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="R41" s="8" t="n">
+      <c r="Q41" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="R41" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S41" s="8" t="n">
+      <c r="S41" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>720.5</v>
-      </c>
-      <c r="U41" s="8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="U41" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V41" s="8" t="n">
+      <c r="V41" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>645.1</v>
+        <v>24.5</v>
       </c>
       <c r="X41" s="8" t="n">
-        <v>29.1</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>1841.1</v>
+        <v>181.1</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>16.7</v>
@@ -3871,68 +3921,68 @@
       <c r="C42" s="3" t="n">
         <v>288.6</v>
       </c>
-      <c r="D42" s="12" t="n">
+      <c r="D42" s="11" t="n">
         <v>30.8</v>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="E42" s="11" t="n">
         <v>20.3</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="F42" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="G42" s="11" t="n">
         <v>10.5</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>188.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>16.6</v>
+        <v>11.6</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K42" s="8" t="n">
-        <v>0.4</v>
+      <c r="K42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M42" s="8" t="n">
-        <v>91.2</v>
+      <c r="M42" s="3" t="n">
+        <v>21.2</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3" t="n">
         <v>30.9</v>
       </c>
       <c r="R42" s="8" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S42" s="8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="S42" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>162</v>
-      </c>
-      <c r="U42" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V42" s="8" t="n">
-        <v>207.1</v>
+      <c r="V42" s="3" t="n">
+        <v>27.1</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X42" s="8" t="n">
-        <v>239.3</v>
+      <c r="X42" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>181.8</v>
@@ -3954,24 +4004,26 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>2311.6</v>
-      </c>
-      <c r="D43" s="12" t="n">
+        <v>311.6</v>
+      </c>
+      <c r="D43" s="11" t="n">
         <v>30.8</v>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="11" t="n">
         <v>21.1</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="F43" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="G43" s="11" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="H43" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="I43" s="3" t="inlineStr"/>
+      <c r="I43" s="8" t="n">
+        <v>41.6</v>
+      </c>
       <c r="J43" s="3" t="n">
         <v>3</v>
       </c>
@@ -3981,47 +4033,47 @@
       <c r="L43" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M43" s="8" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="N43" s="8" t="n">
+      <c r="M43" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="N43" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q43" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="8" t="n">
+      <c r="R43" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="S43" s="8" t="n">
+      <c r="S43" s="3" t="n">
         <v>24</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>2.1</v>
+        <v>8.1</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>24.8</v>
+        <v>24</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="X43" s="3" t="n">
-        <v>35.4</v>
+      <c r="X43" s="8" t="n">
+        <v>25.2</v>
       </c>
       <c r="Y43" s="3" t="n">
         <v>184.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>14.6</v>
+        <v>16.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4037,9 +4089,15 @@
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="3" t="inlineStr"/>
+      <c r="D44" s="11" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>25</v>
+      </c>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -4074,54 +4132,66 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1722.7</v>
-      </c>
-      <c r="D45" s="16" t="inlineStr"/>
-      <c r="E45" s="16" t="inlineStr"/>
-      <c r="F45" s="16" t="inlineStr"/>
+        <v>18422.4</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>123</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>152.4</v>
+      </c>
       <c r="G45" s="3" t="n">
-        <v>6.1</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>293.6</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.8</v>
+        <v>829.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>164.9</v>
+        <v>1164.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="n">
+        <v>52.2</v>
+      </c>
       <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>191.8</v>
+        <v>14.4</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>146.2</v>
+        <v>8406.200000000001</v>
       </c>
       <c r="R45" s="3" t="inlineStr"/>
-      <c r="S45" s="3" t="inlineStr"/>
+      <c r="S45" s="3" t="n">
+        <v>22222.4</v>
+      </c>
       <c r="T45" s="3" t="n">
-        <v>341.4</v>
+        <v>348.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>1668</v>
+        <v>66.8</v>
       </c>
       <c r="V45" s="3" t="inlineStr"/>
-      <c r="W45" s="3" t="inlineStr"/>
+      <c r="W45" s="3" t="n">
+        <v>12012.2</v>
+      </c>
       <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>992.3</v>
+        <v>14224.2</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>198.5</v>
+        <v>1082.9</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4139,72 +4209,72 @@
       <c r="C46" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D46" s="12" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E46" s="12" t="n">
+      <c r="D46" s="11" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E46" s="11" t="n">
         <v>20.5</v>
       </c>
-      <c r="F46" s="12" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G46" s="12" t="n">
+      <c r="F46" s="11" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G46" s="11" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="8" t="n">
+      <c r="H46" s="3" t="n">
         <v>88.7</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="J46" s="3" t="n">
-        <v>3</v>
+      <c r="J46" s="8" t="n">
+        <v>53</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="M46" s="8" t="n">
-        <v>20.6</v>
+      <c r="M46" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>198.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q46" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q46" s="3" t="n">
         <v>29.3</v>
       </c>
-      <c r="R46" s="3" t="n">
-        <v>645.1</v>
+      <c r="R46" s="8" t="n">
+        <v>24.2</v>
       </c>
       <c r="S46" s="8" t="n">
-        <v>27.7</v>
+        <v>71.7</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>168.3</v>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v>292.2</v>
+        <v>68.3</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>13.2</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="W46" s="8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="W46" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X46" s="8" t="n">
+      <c r="X46" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>18.5</v>
+        <v>128.5</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>7.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_recalc_multi_day_tot_and_avgs.xlsx
@@ -828,7 +828,7 @@
       <c r="J4" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
@@ -913,7 +913,7 @@
       <c r="J5" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="L5" s="3" t="n">
@@ -998,7 +998,7 @@
       <c r="J6" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
@@ -1083,7 +1083,7 @@
       <c r="J7" s="8" t="n">
         <v>2.1</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="9" t="n">
         <v>0.1</v>
       </c>
       <c r="L7" s="3" t="n">
@@ -1168,7 +1168,7 @@
       <c r="J8" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       <c r="J9" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1424,7 +1424,7 @@
       <c r="J11" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
@@ -1509,7 +1509,7 @@
       <c r="J12" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="9" t="n">
         <v>4.8</v>
       </c>
       <c r="L12" s="3" t="n">
@@ -1594,7 +1594,7 @@
       <c r="J13" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.6</v>
       </c>
       <c r="L13" s="3" t="n">
@@ -1679,7 +1679,7 @@
       <c r="J14" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="3" t="n">
@@ -1764,7 +1764,7 @@
       <c r="J15" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
@@ -1849,7 +1849,7 @@
       <c r="J16" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="9" t="n">
         <v>16.4</v>
       </c>
       <c r="L16" s="3" t="n">
@@ -2019,7 +2019,7 @@
       <c r="J18" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="8" t="n">
@@ -2104,7 +2104,7 @@
       <c r="J19" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="9" t="n">
         <v>4.2</v>
       </c>
       <c r="L19" s="3" t="n">
@@ -2189,7 +2189,7 @@
       <c r="J20" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="9" t="n">
         <v>2.2</v>
       </c>
       <c r="L20" s="3" t="n">
@@ -2274,7 +2274,7 @@
       <c r="J21" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="8" t="n">
@@ -2359,7 +2359,7 @@
       <c r="J22" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="9" t="n">
         <v>0.1</v>
       </c>
       <c r="L22" s="8" t="n">
@@ -2444,7 +2444,7 @@
       <c r="J23" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="9" t="n">
         <v>6.5</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -3025,7 +3025,7 @@
       <c r="J30" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="21" t="n">
         <v>23.7</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3614,7 +3614,7 @@
       <c r="J37" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="21" t="n">
         <v>17.9</v>
       </c>
       <c r="L37" s="3" t="n">
@@ -4246,7 +4246,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J45" s="3" t="n"/>
-      <c r="K45" s="3" t="n"/>
+      <c r="K45" s="14" t="n"/>
       <c r="L45" s="3" t="n"/>
       <c r="M45" s="3" t="n">
         <v>10.6</v>
